--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A994"/>
+  <dimension ref="A1:A995"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5369,9 +5369,14 @@
         <v/>
       </c>
     </row>
+    <row r="995">
+      <c r="A995" t="str">
+        <v>AGRO.BA</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A994"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A995"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A995"/>
+  <dimension ref="A1:A996"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5374,9 +5374,14 @@
         <v>AGRO.BA</v>
       </c>
     </row>
+    <row r="996">
+      <c r="A996" t="str">
+        <v>SEMI.BA</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A995"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A996"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A996"/>
+  <dimension ref="A1:A995"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2246,302 +2246,302 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>CELU</v>
+        <v>CECO2</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>CECO2</v>
+        <v>ETHA</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>ETHA</v>
+        <v>IBIT</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>IBIT</v>
+        <v>LAC</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>LAC</v>
+        <v>DIVIDENDOS</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>DIVIDENDOS</v>
+        <v>PNZIF</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>PNZIF</v>
+        <v>ASML</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>ASML</v>
+        <v>TEAM</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>TEAM</v>
+        <v>AI</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>AI</v>
+        <v>CLS</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>CLS</v>
+        <v>CEG</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>CEG</v>
+        <v>DECK</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>DECK</v>
+        <v>RGTI</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>RGTI</v>
+        <v>NOW</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>NOW</v>
+        <v>TEM</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>TEM</v>
+        <v>PATH</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>PATH</v>
+        <v>VRTX</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>VRTX</v>
+        <v>VST</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>VST</v>
+        <v>USO</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>USO</v>
+        <v>EFA</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>EFA</v>
+        <v>IEMG</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>IEMG</v>
+        <v>ACWI</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>ACWI</v>
+        <v>GDX</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>GDX</v>
+        <v>HOOD</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>HOOD</v>
+        <v>CRWV</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>CRWV</v>
+        <v>OKLO</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>OKLO</v>
+        <v>RKLB</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>RKLB</v>
+        <v>ALAB</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ALAB</v>
+        <v>ASTS</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>ASTS</v>
+        <v>IREN</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>IREN</v>
+        <v>ECL</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>ECL</v>
+        <v>SPHQ</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>SPHQ</v>
+        <v>EFECTIVO</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>EFECTIVO</v>
+        <v>URA</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>URA</v>
+        <v>COPX</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>COPX</v>
+        <v>ILF</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>ILF</v>
+        <v>ESGU</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>ESGU</v>
+        <v>IVV</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>IVV</v>
+        <v>BMNR</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>BMNR</v>
+        <v>BX</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>BX</v>
+        <v>RSP</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>RSP</v>
+        <v>EWI</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>EWI</v>
+        <v>XME</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>XME</v>
+        <v>ICLN</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ICLN</v>
+        <v>CRWD</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>CRWD</v>
+        <v>ANET</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>ANET</v>
+        <v>O</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>O</v>
+        <v>GLNG</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>GLNG</v>
+        <v>SNDK</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>SNDK</v>
+        <v>NBIS</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>NBIS</v>
+        <v>HIMS</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>HIMS</v>
+        <v>ONDS</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>ONDS</v>
+        <v>COP</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>COP</v>
+        <v>NEE</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>NEE</v>
+        <v>MP</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>MP</v>
+        <v>CCJ</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>CCJ</v>
+        <v>FISV</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>FISV</v>
+        <v>KEEL</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>KEEL</v>
+        <v>NVO</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>NVO</v>
+        <v/>
       </c>
     </row>
     <row r="430">
@@ -5366,22 +5366,17 @@
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v/>
+        <v>AGRO.BA</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>AGRO.BA</v>
-      </c>
-    </row>
-    <row r="996">
-      <c r="A996" t="str">
         <v>SEMI.BA</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A996"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A995"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A995"/>
+  <dimension ref="A1:A996"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5374,9 +5374,14 @@
         <v>SEMI.BA</v>
       </c>
     </row>
+    <row r="996">
+      <c r="A996" t="str">
+        <v>EWY</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A995"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A996"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A996"/>
+  <dimension ref="A1:A997"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5379,9 +5379,14 @@
         <v>EWY</v>
       </c>
     </row>
+    <row r="997">
+      <c r="A997" t="str">
+        <v>SPCX</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A996"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A997"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -1,34 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,4733 +351,5032 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A996"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A995"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Código</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
+      <c r="A2" t="str">
+        <v>MRNA</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BIOX</t>
-        </is>
+      <c r="A3" t="str">
+        <v>BIOX</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HSY</t>
-        </is>
+      <c r="A4" t="str">
+        <v>HSY</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>FMX</t>
-        </is>
+      <c r="A5" t="str">
+        <v>FMX</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LND</t>
-        </is>
+      <c r="A6" t="str">
+        <v>LND</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RBLX</t>
-        </is>
+      <c r="A7" t="str">
+        <v>RBLX</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
+      <c r="A8" t="str">
+        <v>FSLR</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EBR</t>
-        </is>
+      <c r="A9" t="str">
+        <v>EBR</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NTES</t>
-        </is>
+      <c r="A10" t="str">
+        <v>NTES</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ABBV</t>
-        </is>
+      <c r="A11" t="str">
+        <v>ABBV</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
+      <c r="A12" t="str">
+        <v>LRCX</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BSBR</t>
-        </is>
+      <c r="A13" t="str">
+        <v>BSBR</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ELP</t>
-        </is>
+      <c r="A14" t="str">
+        <v>ELP</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SONY</t>
-        </is>
+      <c r="A15" t="str">
+        <v>SONY</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>UGP</t>
-        </is>
+      <c r="A16" t="str">
+        <v>UGP</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STLA</t>
-        </is>
+      <c r="A17" t="str">
+        <v>STLA</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTE</t>
-        </is>
+      <c r="A18" t="str">
+        <v>TTE</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GGB</t>
-        </is>
+      <c r="A19" t="str">
+        <v>GGB</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ITUB</t>
-        </is>
+      <c r="A20" t="str">
+        <v>ITUB</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MRK</t>
-        </is>
+      <c r="A21" t="str">
+        <v>MRK</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AMAT</t>
-        </is>
+      <c r="A22" t="str">
+        <v>AMAT</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NIO</t>
-        </is>
+      <c r="A23" t="str">
+        <v>NIO</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TIMB</t>
-        </is>
+      <c r="A24" t="str">
+        <v>TIMB</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PAGS</t>
-        </is>
+      <c r="A25" t="str">
+        <v>PAGS</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TM</t>
-        </is>
+      <c r="A26" t="str">
+        <v>TM</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TEN</t>
-        </is>
+      <c r="A27" t="str">
+        <v>TEN</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ADBE</t>
-        </is>
+      <c r="A28" t="str">
+        <v>ADBE</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
+      <c r="A29" t="str">
+        <v>NG</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
+      <c r="A30" t="str">
+        <v>IP</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>SDA</t>
-        </is>
+      <c r="A31" t="str">
+        <v>SDA</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>EWZ</t>
-        </is>
+      <c r="A32" t="str">
+        <v>EWZ</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
+      <c r="A33" t="str">
+        <v>TSLA</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>GRMN</t>
-        </is>
+      <c r="A34" t="str">
+        <v>GRMN</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>PBR</t>
-        </is>
+      <c r="A35" t="str">
+        <v>PBR</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>SID</t>
-        </is>
+      <c r="A36" t="str">
+        <v>SID</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>MDLZ</t>
-        </is>
+      <c r="A37" t="str">
+        <v>MDLZ</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>GPRK</t>
-        </is>
+      <c r="A38" t="str">
+        <v>GPRK</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>OXY</t>
-        </is>
+      <c r="A39" t="str">
+        <v>OXY</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
+      <c r="A40" t="str">
+        <v>HAL</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>BIDU</t>
-        </is>
+      <c r="A41" t="str">
+        <v>BIDU</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>UNH</t>
-        </is>
+      <c r="A42" t="str">
+        <v>UNH</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
+      <c r="A43" t="str">
+        <v>NFLX</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>IBN</t>
-        </is>
+      <c r="A44" t="str">
+        <v>IBN</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>YY</t>
-        </is>
+      <c r="A45" t="str">
+        <v>YY</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>HMC</t>
-        </is>
+      <c r="A46" t="str">
+        <v>HMC</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
+      <c r="A47" t="str">
+        <v>RIO</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>ETSY</t>
-        </is>
+      <c r="A48" t="str">
+        <v>ETSY</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>ABEV</t>
-        </is>
+      <c r="A49" t="str">
+        <v>ABEV</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>UL</t>
-        </is>
+      <c r="A50" t="str">
+        <v>UL</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>JMIA</t>
-        </is>
+      <c r="A51" t="str">
+        <v>JMIA</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>SHEL</t>
-        </is>
+      <c r="A52" t="str">
+        <v>SHEL</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
+      <c r="A53" t="str">
+        <v>E</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BITF</t>
-        </is>
+      <c r="A54" t="str">
+        <v>BITF</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AAP</t>
-        </is>
+      <c r="A55" t="str">
+        <v>AAP</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>BIIB</t>
-        </is>
+      <c r="A56" t="str">
+        <v>BIIB</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STNE</t>
-        </is>
+      <c r="A57" t="str">
+        <v>STNE</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
+      <c r="A58" t="str">
+        <v>KO</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>HDB</t>
-        </is>
+      <c r="A59" t="str">
+        <v>HDB</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
+      <c r="A60" t="str">
+        <v>VALE</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
+      <c r="A61" t="str">
+        <v>UNP</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
+      <c r="A62" t="str">
+        <v>MSFT</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
+      <c r="A63" t="str">
+        <v>AMD</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>AZN</t>
-        </is>
+      <c r="A64" t="str">
+        <v>AZN</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>BHP</t>
-        </is>
+      <c r="A65" t="str">
+        <v>BHP</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>SUZ</t>
-        </is>
+      <c r="A66" t="str">
+        <v>SUZ</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>SATL</t>
-        </is>
+      <c r="A67" t="str">
+        <v>SATL</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>TXN</t>
-        </is>
+      <c r="A68" t="str">
+        <v>TXN</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>VIV</t>
-        </is>
+      <c r="A69" t="str">
+        <v>VIV</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
+      <c r="A70" t="str">
+        <v>AMGN</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>SYY</t>
-        </is>
+      <c r="A71" t="str">
+        <v>SYY</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>VOD</t>
-        </is>
+      <c r="A72" t="str">
+        <v>VOD</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>SBS</t>
-        </is>
+      <c r="A73" t="str">
+        <v>SBS</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BRFS</t>
-        </is>
+      <c r="A74" t="str">
+        <v>BRFS</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MOS</t>
-        </is>
+      <c r="A75" t="str">
+        <v>MOS</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
+      <c r="A76" t="str">
+        <v>COST</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>NGG</t>
-        </is>
+      <c r="A77" t="str">
+        <v>NGG</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>TMO</t>
-        </is>
+      <c r="A78" t="str">
+        <v>TMO</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>BBD</t>
-        </is>
+      <c r="A79" t="str">
+        <v>BBD</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
+      <c r="A80" t="str">
+        <v>INFY</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>DOW</t>
-        </is>
+      <c r="A81" t="str">
+        <v>DOW</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>BABA</t>
-        </is>
+      <c r="A82" t="str">
+        <v>BABA</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>CDE</t>
-        </is>
+      <c r="A83" t="str">
+        <v>CDE</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SWKS</t>
-        </is>
+      <c r="A84" t="str">
+        <v>SWKS</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>ASR</t>
-        </is>
+      <c r="A85" t="str">
+        <v>ASR</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>INTC</t>
-        </is>
+      <c r="A86" t="str">
+        <v>INTC</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>ADI</t>
-        </is>
+      <c r="A87" t="str">
+        <v>ADI</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>LOMA</t>
-        </is>
+      <c r="A88" t="str">
+        <v>LOMA</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>PSX</t>
-        </is>
+      <c r="A89" t="str">
+        <v>PSX</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>HSBC</t>
-        </is>
+      <c r="A90" t="str">
+        <v>HSBC</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>XP</t>
-        </is>
+      <c r="A91" t="str">
+        <v>XP</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>FCX</t>
-        </is>
+      <c r="A92" t="str">
+        <v>FCX</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>BBAR</t>
-        </is>
+      <c r="A93" t="str">
+        <v>BBAR</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>ERJ</t>
-        </is>
+      <c r="A94" t="str">
+        <v>ERJ</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>EEM</t>
-        </is>
+      <c r="A95" t="str">
+        <v>EEM</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>VIST</t>
-        </is>
+      <c r="A96" t="str">
+        <v>VIST</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
+      <c r="A97" t="str">
+        <v>NKE</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
+      <c r="A98" t="str">
+        <v>SBUX</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
+      <c r="A99" t="str">
+        <v>XLE</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
+      <c r="A100" t="str">
+        <v>PG</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>AVY</t>
-        </is>
+      <c r="A101" t="str">
+        <v>AVY</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>SNAP</t>
-        </is>
+      <c r="A102" t="str">
+        <v>SNAP</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>URBN</t>
-        </is>
+      <c r="A103" t="str">
+        <v>URBN</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>VZ</t>
-        </is>
+      <c r="A104" t="str">
+        <v>VZ</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
+      <c r="A105" t="str">
+        <v>JD</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
+      <c r="A106" t="str">
+        <v>XOM</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>QCOM</t>
-        </is>
+      <c r="A107" t="str">
+        <v>QCOM</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>PHG</t>
-        </is>
+      <c r="A108" t="str">
+        <v>PHG</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>CEPU</t>
-        </is>
+      <c r="A109" t="str">
+        <v>CEPU</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>CAH</t>
-        </is>
+      <c r="A110" t="str">
+        <v>CAH</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>SCCO</t>
-        </is>
+      <c r="A111" t="str">
+        <v>SCCO</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
+      <c r="A112" t="str">
+        <v>NU</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>TGT</t>
-        </is>
+      <c r="A113" t="str">
+        <v>TGT</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>VRSN</t>
-        </is>
+      <c r="A114" t="str">
+        <v>VRSN</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
+      <c r="A115" t="str">
+        <v>AMZN</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>ROST</t>
-        </is>
+      <c r="A116" t="str">
+        <v>ROST</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>PSO</t>
-        </is>
+      <c r="A117" t="str">
+        <v>PSO</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>MELI</t>
-        </is>
+      <c r="A118" t="str">
+        <v>MELI</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>PBI</t>
-        </is>
+      <c r="A119" t="str">
+        <v>PBI</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>PINS</t>
-        </is>
+      <c r="A120" t="str">
+        <v>PINS</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>ARKK</t>
-        </is>
+      <c r="A121" t="str">
+        <v>ARKK</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>GOLD</t>
-        </is>
+      <c r="A122" t="str">
+        <v>GOLD</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>EBAY</t>
-        </is>
+      <c r="A123" t="str">
+        <v>EBAY</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>SUPV</t>
-        </is>
+      <c r="A124" t="str">
+        <v>SUPV</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>SPGI</t>
-        </is>
+      <c r="A125" t="str">
+        <v>SPGI</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>ARCO</t>
-        </is>
+      <c r="A126" t="str">
+        <v>ARCO</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
+      <c r="A127" t="str">
+        <v>HL</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>SNOW</t>
-        </is>
+      <c r="A128" t="str">
+        <v>SNOW</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="A129" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
+      <c r="A130" t="str">
+        <v>UBER</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>IFF</t>
-        </is>
+      <c r="A131" t="str">
+        <v>IFF</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
+      <c r="A132" t="str">
+        <v>T</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
+      <c r="A133" t="str">
+        <v>PEP</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>MMM</t>
-        </is>
+      <c r="A134" t="str">
+        <v>MMM</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>MFG</t>
-        </is>
+      <c r="A135" t="str">
+        <v>MFG</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
+      <c r="A136" t="str">
+        <v>SAP</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>BMA</t>
-        </is>
+      <c r="A137" t="str">
+        <v>BMA</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>YELP</t>
-        </is>
+      <c r="A138" t="str">
+        <v>YELP</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>TCOM</t>
-        </is>
+      <c r="A139" t="str">
+        <v>TCOM</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>EDN</t>
-        </is>
+      <c r="A140" t="str">
+        <v>EDN</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
+      <c r="A141" t="str">
+        <v>MDT</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
+      <c r="A142" t="str">
+        <v>META</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>NVS</t>
-        </is>
+      <c r="A143" t="str">
+        <v>NVS</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>HUT</t>
-        </is>
+      <c r="A144" t="str">
+        <v>HUT</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
+      <c r="A145" t="str">
+        <v>WMT</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>CVX</t>
-        </is>
+      <c r="A146" t="str">
+        <v>CVX</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
+      <c r="A147" t="str">
+        <v>QQQ</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>RACE</t>
-        </is>
+      <c r="A148" t="str">
+        <v>RACE</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
+      <c r="A149" t="str">
+        <v>AAPL</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>ZM</t>
-        </is>
+      <c r="A150" t="str">
+        <v>ZM</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>DEO</t>
-        </is>
+      <c r="A151" t="str">
+        <v>DEO</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>CAAP</t>
-        </is>
+      <c r="A152" t="str">
+        <v>CAAP</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A153" t="str">
+        <v>X</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>AEG</t>
-        </is>
+      <c r="A154" t="str">
+        <v>AEG</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>TRIP</t>
-        </is>
+      <c r="A155" t="str">
+        <v>TRIP</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>SPOT</t>
-        </is>
+      <c r="A156" t="str">
+        <v>SPOT</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
+      <c r="A157" t="str">
+        <v>AVGO</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
+      <c r="A158" t="str">
+        <v>F</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>PAAS</t>
-        </is>
+      <c r="A159" t="str">
+        <v>PAAS</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
+      <c r="A160" t="str">
+        <v>CAT</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
+      <c r="A161" t="str">
+        <v>JNJ</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
+      <c r="A162" t="str">
+        <v>SHOP</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>JCI</t>
-        </is>
+      <c r="A163" t="str">
+        <v>JCI</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>MUFG</t>
-        </is>
+      <c r="A164" t="str">
+        <v>MUFG</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>LVS</t>
-        </is>
+      <c r="A165" t="str">
+        <v>LVS</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>AMX</t>
-        </is>
+      <c r="A166" t="str">
+        <v>AMX</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>ROKU</t>
-        </is>
+      <c r="A167" t="str">
+        <v>ROKU</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>MSTR</t>
-        </is>
+      <c r="A168" t="str">
+        <v>MSTR</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>GLW</t>
-        </is>
+      <c r="A169" t="str">
+        <v>GLW</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>LYG</t>
-        </is>
+      <c r="A170" t="str">
+        <v>LYG</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
+      <c r="A171" t="str">
+        <v>GM</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
+      <c r="A172" t="str">
+        <v>ABT</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
+      <c r="A173" t="str">
+        <v>COIN</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>KMB</t>
-        </is>
+      <c r="A174" t="str">
+        <v>KMB</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
+      <c r="A175" t="str">
+        <v>NVDA</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>HPQ</t>
-        </is>
+      <c r="A176" t="str">
+        <v>HPQ</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>MRVL</t>
-        </is>
+      <c r="A177" t="str">
+        <v>MRVL</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
+      <c r="A178" t="str">
+        <v>IWM</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
+      <c r="A179" t="str">
+        <v>LAC</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
+      <c r="A180" t="str">
+        <v>LAC</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>RTX</t>
-        </is>
+      <c r="A181" t="str">
+        <v>RTX</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
+      <c r="A182" t="str">
+        <v>GE</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>ABNB</t>
-        </is>
+      <c r="A183" t="str">
+        <v>ABNB</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>LMT</t>
-        </is>
+      <c r="A184" t="str">
+        <v>LMT</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
+      <c r="A185" t="str">
+        <v>MU</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>NUE</t>
-        </is>
+      <c r="A186" t="str">
+        <v>NUE</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>KGC</t>
-        </is>
+      <c r="A187" t="str">
+        <v>KGC</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
+      <c r="A188" t="str">
+        <v>PLTR</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
+      <c r="A189" t="str">
+        <v>SPY</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>HMY</t>
-        </is>
+      <c r="A190" t="str">
+        <v>HMY</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
+      <c r="A191" t="str">
+        <v>PANW</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
+      <c r="A192" t="str">
+        <v>CRM</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>SPCE</t>
-        </is>
+      <c r="A193" t="str">
+        <v>SPCE</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>DESP</t>
-        </is>
+      <c r="A194" t="str">
+        <v>DESP</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>GLOB</t>
-        </is>
+      <c r="A195" t="str">
+        <v>GLOB</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
+      <c r="A196" t="str">
+        <v>V</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>ORCL</t>
-        </is>
+      <c r="A197" t="str">
+        <v>ORCL</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>GGAL</t>
-        </is>
+      <c r="A198" t="str">
+        <v>GGAL</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
+      <c r="A199" t="str">
+        <v>SE</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>DIA</t>
-        </is>
+      <c r="A200" t="str">
+        <v>DIA</v>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>AIG</t>
-        </is>
+      <c r="A201" t="str">
+        <v>AIG</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>NEM</t>
-        </is>
+      <c r="A202" t="str">
+        <v>NEM</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>ERIC</t>
-        </is>
+      <c r="A203" t="str">
+        <v>ERIC</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>GFI</t>
-        </is>
+      <c r="A204" t="str">
+        <v>GFI</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
+      <c r="A205" t="str">
+        <v>JPM</v>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
+      <c r="A206" t="str">
+        <v>GS</v>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
+      <c r="A207" t="str">
+        <v>BAC</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
+      <c r="A208" t="str">
+        <v>SQ</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>TWLO</t>
-        </is>
+      <c r="A209" t="str">
+        <v>TWLO</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>RIOT</t>
-        </is>
+      <c r="A210" t="str">
+        <v>RIOT</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
+      <c r="A211" t="str">
+        <v>DAL</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>ADP</t>
-        </is>
+      <c r="A212" t="str">
+        <v>ADP</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>PAM</t>
-        </is>
+      <c r="A213" t="str">
+        <v>PAM</v>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>PAM</t>
-        </is>
+      <c r="A214" t="str">
+        <v>PAM</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>UPST</t>
-        </is>
+      <c r="A215" t="str">
+        <v>UPST</v>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
+      <c r="A216" t="str">
+        <v>MA</v>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
+      <c r="A217" t="str">
+        <v>IBM</v>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>GILD</t>
-        </is>
+      <c r="A218" t="str">
+        <v>GILD</v>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>AAL</t>
-        </is>
+      <c r="A219" t="str">
+        <v>AAL</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>XLF</t>
-        </is>
+      <c r="A220" t="str">
+        <v>XLF</v>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>BKNG</t>
-        </is>
+      <c r="A221" t="str">
+        <v>BKNG</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>CCL</t>
-        </is>
+      <c r="A222" t="str">
+        <v>CCL</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>TSM</t>
-        </is>
+      <c r="A223" t="str">
+        <v>TSM</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>USB</t>
-        </is>
+      <c r="A224" t="str">
+        <v>USB</v>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
+      <c r="A225" t="str">
+        <v>HON</v>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>PCAR</t>
-        </is>
+      <c r="A226" t="str">
+        <v>PCAR</v>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>WFC</t>
-        </is>
+      <c r="A227" t="str">
+        <v>WFC</v>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>SCHW</t>
-        </is>
+      <c r="A228" t="str">
+        <v>SCHW</v>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>MCD</t>
-        </is>
+      <c r="A229" t="str">
+        <v>MCD</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>DOCU</t>
-        </is>
+      <c r="A230" t="str">
+        <v>DOCU</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>TMUS</t>
-        </is>
+      <c r="A231" t="str">
+        <v>TMUS</v>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
+      <c r="A232" t="str">
+        <v>CSCO</v>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>MSI</t>
-        </is>
+      <c r="A233" t="str">
+        <v>MSI</v>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>SNA</t>
-        </is>
+      <c r="A234" t="str">
+        <v>SNA</v>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>UAL</t>
-        </is>
+      <c r="A235" t="str">
+        <v>UAL</v>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>AABA</t>
-        </is>
+      <c r="A236" t="str">
+        <v>AABA</v>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
+      <c r="A237" t="str">
+        <v>ACN</v>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>ADGO</t>
-        </is>
+      <c r="A238" t="str">
+        <v>ADGO</v>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>ADS</t>
-        </is>
+      <c r="A239" t="str">
+        <v>ADS</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>AEM</t>
-        </is>
+      <c r="A240" t="str">
+        <v>AEM</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>AKO.B</t>
-        </is>
+      <c r="A241" t="str">
+        <v>AKO.B</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>AL29</t>
-        </is>
+      <c r="A242" t="str">
+        <v>AL29</v>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>AL30</t>
-        </is>
+      <c r="A243" t="str">
+        <v>AL30</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>ALUA</t>
-        </is>
+      <c r="A244" t="str">
+        <v>ALUA</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>ANF</t>
-        </is>
+      <c r="A245" t="str">
+        <v>ANF</v>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>AOCA</t>
-        </is>
+      <c r="A246" t="str">
+        <v>AOCA</v>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>ATAD</t>
-        </is>
+      <c r="A247" t="str">
+        <v>ATAD</v>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>AUY</t>
-        </is>
+      <c r="A248" t="str">
+        <v>AUY</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
+      <c r="A249" t="str">
+        <v>AXP</v>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
+      <c r="A250" t="str">
+        <v>BA</v>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>BA.C</t>
-        </is>
+      <c r="A251" t="str">
+        <v>BA.C</v>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>BAK</t>
-        </is>
+      <c r="A252" t="str">
+        <v>BAK</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>BAS</t>
-        </is>
+      <c r="A253" t="str">
+        <v>BAS</v>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
+      <c r="A254" t="str">
+        <v>BB</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>BBAS3</t>
-        </is>
+      <c r="A255" t="str">
+        <v>BBAS3</v>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>BBV</t>
-        </is>
+      <c r="A256" t="str">
+        <v>BBV</v>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>BCS</t>
-        </is>
+      <c r="A257" t="str">
+        <v>BCS</v>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>BK</t>
-        </is>
+      <c r="A258" t="str">
+        <v>BK</v>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>BMY</t>
-        </is>
+      <c r="A259" t="str">
+        <v>BMY</v>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>BNG</t>
-        </is>
+      <c r="A260" t="str">
+        <v>BNG</v>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>BP</t>
-        </is>
+      <c r="A261" t="str">
+        <v>BP</v>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>BRKB</t>
-        </is>
+      <c r="A262" t="str">
+        <v>BRKB</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>BSN</t>
-        </is>
+      <c r="A263" t="str">
+        <v>BSN</v>
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>BYMA</t>
-        </is>
+      <c r="A264" t="str">
+        <v>BYMA</v>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>CAJ</t>
-        </is>
+      <c r="A265" t="str">
+        <v>CAJ</v>
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
+      <c r="A266" t="str">
+        <v>CAR</v>
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>CBRD</t>
-        </is>
+      <c r="A267" t="str">
+        <v>CL</v>
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
+      <c r="A268" t="str">
+        <v>COME</v>
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>COME</t>
-        </is>
+      <c r="A269" t="str">
+        <v>CRES</v>
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>CRES</t>
-        </is>
+      <c r="A270" t="str">
+        <v>CS</v>
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
+      <c r="A271" t="str">
+        <v>CVS</v>
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
+      <c r="A272" t="str">
+        <v>CX</v>
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>CX</t>
-        </is>
+      <c r="A273" t="str">
+        <v>DD</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>DD</t>
-        </is>
+      <c r="A274" t="str">
+        <v>DE</v>
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="A275" t="str">
+        <v>DIS</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
+      <c r="A276" t="str">
+        <v>DTEA</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>DTEA</t>
-        </is>
+      <c r="A277" t="str">
+        <v>EA</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
+      <c r="A278" t="str">
+        <v>EFX</v>
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
+      <c r="A279" t="str">
+        <v>EOAN</v>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>EOAN</t>
-        </is>
+      <c r="A280" t="str">
+        <v>FDX</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
+      <c r="A281" t="str">
+        <v>FMCC</v>
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>FMCC</t>
-        </is>
+      <c r="A282" t="str">
+        <v>FNMA</v>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>FNMA</t>
-        </is>
+      <c r="A283" t="str">
+        <v>GD 29</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>GD 29</t>
-        </is>
+      <c r="A284" t="str">
+        <v>GOOGL</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
+      <c r="A285" t="str">
+        <v>GSK</v>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>GSK</t>
-        </is>
+      <c r="A286" t="str">
+        <v>HAPV3</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>HAPV3</t>
-        </is>
+      <c r="A287" t="str">
+        <v>HD</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
+      <c r="A288" t="str">
+        <v>HHPD</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>HHPD</t>
-        </is>
+      <c r="A289" t="str">
+        <v>HNPIY</v>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>HNPIY</t>
-        </is>
+      <c r="A290" t="str">
+        <v>HOG</v>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>HOG</t>
-        </is>
+      <c r="A291" t="str">
+        <v>HWM</v>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>HWM</t>
-        </is>
+      <c r="A292" t="str">
+        <v>ING</v>
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>ING</t>
-        </is>
+      <c r="A293" t="str">
+        <v>IRSA</v>
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>IRSA</t>
-        </is>
+      <c r="A294" t="str">
+        <v>KB</v>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>KB</t>
-        </is>
+      <c r="A295" t="str">
+        <v>KEP</v>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>KEP</t>
-        </is>
+      <c r="A296" t="str">
+        <v>KOFM</v>
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>KOFM</t>
-        </is>
+      <c r="A297" t="str">
+        <v>LFC</v>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>LFC</t>
-        </is>
+      <c r="A298" t="str">
+        <v>LLY</v>
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>LLY</t>
-        </is>
+      <c r="A299" t="str">
+        <v>LREN3</v>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>LREN3</t>
-        </is>
+      <c r="A300" t="str">
+        <v>MBT</v>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>MBT</t>
-        </is>
+      <c r="A301" t="str">
+        <v>METR</v>
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>METR</t>
-        </is>
+      <c r="A302" t="str">
+        <v>MGLU3</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>MGLU3</t>
-        </is>
+      <c r="A303" t="str">
+        <v>MMC</v>
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>MMC</t>
-        </is>
+      <c r="A304" t="str">
+        <v>MO</v>
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
+      <c r="A305" t="str">
+        <v>MORI</v>
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>MORI</t>
-        </is>
+      <c r="A306" t="str">
+        <v>MUX</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>MUX</t>
-        </is>
+      <c r="A307" t="str">
+        <v>NEC1</v>
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>NEC1</t>
-        </is>
+      <c r="A308" t="str">
+        <v>NMR</v>
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>NMR</t>
-        </is>
+      <c r="A309" t="str">
+        <v>NOKA</v>
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>NOKA</t>
-        </is>
+      <c r="A310" t="str">
+        <v>NSAN</v>
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>NSAN</t>
-        </is>
+      <c r="A311" t="str">
+        <v>NTCO</v>
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>NTCO</t>
-        </is>
+      <c r="A312" t="str">
+        <v>ORAN</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>ORAN</t>
-        </is>
+      <c r="A313" t="str">
+        <v>PAC</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>PAC</t>
-        </is>
+      <c r="A314" t="str">
+        <v>PAMP</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>PAMP</t>
-        </is>
+      <c r="A315" t="str">
+        <v>PCRF</v>
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>PCRF</t>
-        </is>
+      <c r="A316" t="str">
+        <v>PFE</v>
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
+      <c r="A317" t="str">
+        <v>PKS</v>
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>PKS</t>
-        </is>
+      <c r="A318" t="str">
+        <v>PM</v>
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
+      <c r="A319" t="str">
+        <v>PRIO3</v>
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>PRIO3</t>
-        </is>
+      <c r="A320" t="str">
+        <v>PTR</v>
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>PTR</t>
-        </is>
+      <c r="A321" t="str">
+        <v>PYPL</v>
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
+      <c r="A322" t="str">
+        <v>RCTB4</v>
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>RCTB4</t>
-        </is>
+      <c r="A323" t="str">
+        <v>RENT3</v>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>RENT3</t>
-        </is>
+      <c r="A324" t="str">
+        <v>SAN</v>
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>SAN</t>
-        </is>
+      <c r="A325" t="str">
+        <v>SHPW</v>
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>SHPW</t>
-        </is>
+      <c r="A326" t="str">
+        <v>SI</v>
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
+      <c r="A327" t="str">
+        <v>SIEGY</v>
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>SIEGY</t>
-        </is>
+      <c r="A328" t="str">
+        <v>SLB</v>
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
+      <c r="A329" t="str">
+        <v>SMSN</v>
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>SMSN</t>
-        </is>
+      <c r="A330" t="str">
+        <v>SNP</v>
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>SNP</t>
-        </is>
+      <c r="A331" t="str">
+        <v>TECO2</v>
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>TECO2</t>
-        </is>
+      <c r="A332" t="str">
+        <v>TEFO</v>
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>TEFO</t>
-        </is>
+      <c r="A333" t="str">
+        <v>TGNO4</v>
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>TGNO4</t>
-        </is>
+      <c r="A334" t="str">
+        <v>TGSU2</v>
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>TGSU2</t>
-        </is>
+      <c r="A335" t="str">
+        <v>TIIAY</v>
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>TIIAY</t>
-        </is>
+      <c r="A336" t="str">
+        <v>TRVV</v>
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>TRVV</t>
-        </is>
+      <c r="A337" t="str">
+        <v>TSMC</v>
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>TSMC</t>
-        </is>
+      <c r="A338" t="str">
+        <v>TTM</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>TTM</t>
-        </is>
+      <c r="A339" t="str">
+        <v>TV</v>
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>TV</t>
-        </is>
+      <c r="A340" t="str">
+        <v>TWTR</v>
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>TWTR</t>
-        </is>
+      <c r="A341" t="str">
+        <v>TXR</v>
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>TXR</t>
-        </is>
+      <c r="A342" t="str">
+        <v>VALO</v>
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>VALO</t>
-        </is>
+      <c r="A343" t="str">
+        <v>WBA</v>
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>WBA</t>
-        </is>
+      <c r="A344" t="str">
+        <v>WBO</v>
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>WBO</t>
-        </is>
+      <c r="A345" t="str">
+        <v>XROX</v>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>XROX</t>
-        </is>
+      <c r="A346" t="str">
+        <v>YPFD</v>
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>YPFD</t>
-        </is>
+      <c r="A347" t="str">
+        <v>YZCA</v>
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>YZCA</t>
-        </is>
+      <c r="A348" t="str">
+        <v>EQNR</v>
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>EQNR</t>
-        </is>
+      <c r="A349" t="str">
+        <v>ARM</v>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>ARM</t>
-        </is>
+      <c r="A350" t="str">
+        <v>BKR</v>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>BKR</t>
-        </is>
+      <c r="A351" t="str">
+        <v>DHR</v>
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>DHR</t>
-        </is>
+      <c r="A352" t="str">
+        <v>GT</v>
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
+      <c r="A353" t="str">
+        <v>ISRG</v>
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>ISRG</t>
-        </is>
+      <c r="A354" t="str">
+        <v>LAAC</v>
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>LAAC</t>
-        </is>
+      <c r="A355" t="str">
+        <v>NXE</v>
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>NXE</t>
-        </is>
+      <c r="A356" t="str">
+        <v>ORLY</v>
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>ORLY</t>
-        </is>
+      <c r="A357" t="str">
+        <v>TJX</v>
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>TJX</t>
-        </is>
+      <c r="A358" t="str">
+        <v>SAMI</v>
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>SAMI</t>
-        </is>
+      <c r="A359" t="str">
+        <v>BHIP</v>
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>BHIP</t>
-        </is>
+      <c r="A360" t="str">
+        <v>SEMI</v>
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>SEMI</t>
-        </is>
+      <c r="A361" t="str">
+        <v>FERR</v>
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>FERR</t>
-        </is>
+      <c r="A362" t="str">
+        <v>AGRO</v>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>AGRO</t>
-        </is>
+      <c r="A363" t="str">
+        <v>IRS</v>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>IRS</t>
-        </is>
+      <c r="A364" t="str">
+        <v>AL 30</v>
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>AL 30</t>
-        </is>
+      <c r="A365" t="str">
+        <v>GD 30</v>
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>GD 30</t>
-        </is>
+      <c r="A366" t="str">
+        <v>AL 29</v>
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>AL 29</t>
-        </is>
+      <c r="A367" t="str">
+        <v>GD29</v>
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>GD29</t>
-        </is>
+      <c r="A368" t="str">
+        <v>CECO2</v>
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>CECO2</t>
-        </is>
+      <c r="A369" t="str">
+        <v>ETHA</v>
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>ETHA</t>
-        </is>
+      <c r="A370" t="str">
+        <v>IBIT</v>
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>IBIT</t>
-        </is>
+      <c r="A371" t="str">
+        <v>LAC</v>
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
+      <c r="A372" t="str">
+        <v>DIVIDENDOS</v>
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>DIVIDENDOS</t>
-        </is>
+      <c r="A373" t="str">
+        <v>PNZIF</v>
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>PNZIF</t>
-        </is>
+      <c r="A374" t="str">
+        <v>ASML</v>
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>ASML</t>
-        </is>
+      <c r="A375" t="str">
+        <v>TEAM</v>
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
+      <c r="A376" t="str">
+        <v>AI</v>
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
+      <c r="A377" t="str">
+        <v>CLS</v>
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>CLS</t>
-        </is>
+      <c r="A378" t="str">
+        <v>CEG</v>
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>CEG</t>
-        </is>
+      <c r="A379" t="str">
+        <v>DECK</v>
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>DECK</t>
-        </is>
+      <c r="A380" t="str">
+        <v>RGTI</v>
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>RGTI</t>
-        </is>
+      <c r="A381" t="str">
+        <v>NOW</v>
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
+      <c r="A382" t="str">
+        <v>TEM</v>
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>TEM</t>
-        </is>
+      <c r="A383" t="str">
+        <v>PATH</v>
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>PATH</t>
-        </is>
+      <c r="A384" t="str">
+        <v>VRTX</v>
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>VRTX</t>
-        </is>
+      <c r="A385" t="str">
+        <v>VST</v>
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>VST</t>
-        </is>
+      <c r="A386" t="str">
+        <v>USO</v>
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
+      <c r="A387" t="str">
+        <v>EFA</v>
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>EFA</t>
-        </is>
+      <c r="A388" t="str">
+        <v>IEMG</v>
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>IEMG</t>
-        </is>
+      <c r="A389" t="str">
+        <v>ACWI</v>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>ACWI</t>
-        </is>
+      <c r="A390" t="str">
+        <v>GDX</v>
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
+      <c r="A391" t="str">
+        <v>HOOD</v>
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
+      <c r="A392" t="str">
+        <v>CRWV</v>
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
+      <c r="A393" t="str">
+        <v>OKLO</v>
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>OKLO</t>
-        </is>
+      <c r="A394" t="str">
+        <v>RKLB</v>
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>RKLB</t>
-        </is>
+      <c r="A395" t="str">
+        <v>ALAB</v>
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>ALAB</t>
-        </is>
+      <c r="A396" t="str">
+        <v>ASTS</v>
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>ASTS</t>
-        </is>
+      <c r="A397" t="str">
+        <v>IREN</v>
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>IREN</t>
-        </is>
+      <c r="A398" t="str">
+        <v>ECL</v>
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>ECL</t>
-        </is>
+      <c r="A399" t="str">
+        <v>SPHQ</v>
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>SPHQ</t>
-        </is>
+      <c r="A400" t="str">
+        <v>EFECTIVO</v>
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>EFECTIVO</t>
-        </is>
+      <c r="A401" t="str">
+        <v>URA</v>
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>URA</t>
-        </is>
+      <c r="A402" t="str">
+        <v>COPX</v>
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>COPX</t>
-        </is>
+      <c r="A403" t="str">
+        <v>ILF</v>
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>ILF</t>
-        </is>
+      <c r="A404" t="str">
+        <v>ESGU</v>
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>ESGU</t>
-        </is>
+      <c r="A405" t="str">
+        <v>IVV</v>
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>IVV</t>
-        </is>
+      <c r="A406" t="str">
+        <v>BMNR</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>BMNR</t>
-        </is>
+      <c r="A407" t="str">
+        <v>BX</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>BX</t>
-        </is>
+      <c r="A408" t="str">
+        <v>RSP</v>
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>RSP</t>
-        </is>
+      <c r="A409" t="str">
+        <v>EWI</v>
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>EWI</t>
-        </is>
+      <c r="A410" t="str">
+        <v>XME</v>
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>XME</t>
-        </is>
+      <c r="A411" t="str">
+        <v>ICLN</v>
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>ICLN</t>
-        </is>
+      <c r="A412" t="str">
+        <v>CRWD</v>
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
+      <c r="A413" t="str">
+        <v>ANET</v>
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>ANET</t>
-        </is>
+      <c r="A414" t="str">
+        <v>O</v>
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="A415" t="str">
+        <v>GLNG</v>
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>GLNG</t>
-        </is>
+      <c r="A416" t="str">
+        <v>SNDK</v>
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>SNDK</t>
-        </is>
+      <c r="A417" t="str">
+        <v>NBIS</v>
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>NBIS</t>
-        </is>
+      <c r="A418" t="str">
+        <v>HIMS</v>
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>HIMS</t>
-        </is>
+      <c r="A419" t="str">
+        <v>ONDS</v>
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>ONDS</t>
-        </is>
+      <c r="A420" t="str">
+        <v>COP</v>
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
+      <c r="A421" t="str">
+        <v>NEE</v>
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>NEE</t>
-        </is>
+      <c r="A422" t="str">
+        <v>MP</v>
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
+      <c r="A423" t="str">
+        <v>CCJ</v>
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>CCJ</t>
-        </is>
+      <c r="A424" t="str">
+        <v>FISV</v>
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>FISV</t>
-        </is>
+      <c r="A425" t="str">
+        <v>KEEL</v>
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>KEEL</t>
-        </is>
+      <c r="A426" t="str">
+        <v>NVO</v>
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>NVO</t>
-        </is>
+      <c r="A427" t="str">
+        <v/>
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr"/>
+      <c r="A428" t="str">
+        <v/>
+      </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr"/>
+      <c r="A429" t="str">
+        <v/>
+      </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr"/>
+      <c r="A430" t="str">
+        <v/>
+      </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr"/>
+      <c r="A431" t="str">
+        <v/>
+      </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr"/>
+      <c r="A432" t="str">
+        <v/>
+      </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr"/>
+      <c r="A433" t="str">
+        <v/>
+      </c>
     </row>
     <row r="434">
-      <c r="A434" t="inlineStr"/>
+      <c r="A434" t="str">
+        <v/>
+      </c>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr"/>
+      <c r="A435" t="str">
+        <v/>
+      </c>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr"/>
+      <c r="A436" t="str">
+        <v/>
+      </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr"/>
+      <c r="A437" t="str">
+        <v/>
+      </c>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr"/>
+      <c r="A438" t="str">
+        <v/>
+      </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr"/>
+      <c r="A439" t="str">
+        <v/>
+      </c>
     </row>
     <row r="440">
-      <c r="A440" t="inlineStr"/>
+      <c r="A440" t="str">
+        <v/>
+      </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr"/>
+      <c r="A441" t="str">
+        <v/>
+      </c>
     </row>
     <row r="442">
-      <c r="A442" t="inlineStr"/>
+      <c r="A442" t="str">
+        <v/>
+      </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr"/>
+      <c r="A443" t="str">
+        <v/>
+      </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr"/>
+      <c r="A444" t="str">
+        <v/>
+      </c>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr"/>
+      <c r="A445" t="str">
+        <v/>
+      </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr"/>
+      <c r="A446" t="str">
+        <v/>
+      </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr"/>
+      <c r="A447" t="str">
+        <v/>
+      </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr"/>
+      <c r="A448" t="str">
+        <v/>
+      </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr"/>
+      <c r="A449" t="str">
+        <v/>
+      </c>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr"/>
+      <c r="A450" t="str">
+        <v/>
+      </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr"/>
+      <c r="A451" t="str">
+        <v/>
+      </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr"/>
+      <c r="A452" t="str">
+        <v/>
+      </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr"/>
+      <c r="A453" t="str">
+        <v/>
+      </c>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr"/>
+      <c r="A454" t="str">
+        <v/>
+      </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr"/>
+      <c r="A455" t="str">
+        <v/>
+      </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr"/>
+      <c r="A456" t="str">
+        <v/>
+      </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr"/>
+      <c r="A457" t="str">
+        <v/>
+      </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr"/>
+      <c r="A458" t="str">
+        <v/>
+      </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr"/>
+      <c r="A459" t="str">
+        <v/>
+      </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr"/>
+      <c r="A460" t="str">
+        <v/>
+      </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr"/>
+      <c r="A461" t="str">
+        <v/>
+      </c>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr"/>
+      <c r="A462" t="str">
+        <v/>
+      </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr"/>
+      <c r="A463" t="str">
+        <v/>
+      </c>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr"/>
+      <c r="A464" t="str">
+        <v/>
+      </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr"/>
+      <c r="A465" t="str">
+        <v/>
+      </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr"/>
+      <c r="A466" t="str">
+        <v/>
+      </c>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr"/>
+      <c r="A467" t="str">
+        <v/>
+      </c>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr"/>
+      <c r="A468" t="str">
+        <v/>
+      </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr"/>
+      <c r="A469" t="str">
+        <v/>
+      </c>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr"/>
+      <c r="A470" t="str">
+        <v/>
+      </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr"/>
+      <c r="A471" t="str">
+        <v/>
+      </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr"/>
+      <c r="A472" t="str">
+        <v/>
+      </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr"/>
+      <c r="A473" t="str">
+        <v/>
+      </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr"/>
+      <c r="A474" t="str">
+        <v/>
+      </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr"/>
+      <c r="A475" t="str">
+        <v/>
+      </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr"/>
+      <c r="A476" t="str">
+        <v/>
+      </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr"/>
+      <c r="A477" t="str">
+        <v/>
+      </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr"/>
+      <c r="A478" t="str">
+        <v/>
+      </c>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr"/>
+      <c r="A479" t="str">
+        <v/>
+      </c>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr"/>
+      <c r="A480" t="str">
+        <v/>
+      </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr"/>
+      <c r="A481" t="str">
+        <v/>
+      </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr"/>
+      <c r="A482" t="str">
+        <v/>
+      </c>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr"/>
+      <c r="A483" t="str">
+        <v/>
+      </c>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr"/>
+      <c r="A484" t="str">
+        <v/>
+      </c>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr"/>
+      <c r="A485" t="str">
+        <v/>
+      </c>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr"/>
+      <c r="A486" t="str">
+        <v/>
+      </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr"/>
+      <c r="A487" t="str">
+        <v/>
+      </c>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr"/>
+      <c r="A488" t="str">
+        <v/>
+      </c>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr"/>
+      <c r="A489" t="str">
+        <v/>
+      </c>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr"/>
+      <c r="A490" t="str">
+        <v/>
+      </c>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr"/>
+      <c r="A491" t="str">
+        <v/>
+      </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr"/>
+      <c r="A492" t="str">
+        <v/>
+      </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr"/>
+      <c r="A493" t="str">
+        <v/>
+      </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr"/>
+      <c r="A494" t="str">
+        <v/>
+      </c>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr"/>
+      <c r="A495" t="str">
+        <v/>
+      </c>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr"/>
+      <c r="A496" t="str">
+        <v/>
+      </c>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr"/>
+      <c r="A497" t="str">
+        <v/>
+      </c>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr"/>
+      <c r="A498" t="str">
+        <v/>
+      </c>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr"/>
+      <c r="A499" t="str">
+        <v/>
+      </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr"/>
+      <c r="A500" t="str">
+        <v/>
+      </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr"/>
+      <c r="A501" t="str">
+        <v/>
+      </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr"/>
+      <c r="A502" t="str">
+        <v/>
+      </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr"/>
+      <c r="A503" t="str">
+        <v/>
+      </c>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr"/>
+      <c r="A504" t="str">
+        <v/>
+      </c>
     </row>
     <row r="505">
-      <c r="A505" t="inlineStr"/>
+      <c r="A505" t="str">
+        <v/>
+      </c>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr"/>
+      <c r="A506" t="str">
+        <v/>
+      </c>
     </row>
     <row r="507">
-      <c r="A507" t="inlineStr"/>
+      <c r="A507" t="str">
+        <v/>
+      </c>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr"/>
+      <c r="A508" t="str">
+        <v/>
+      </c>
     </row>
     <row r="509">
-      <c r="A509" t="inlineStr"/>
+      <c r="A509" t="str">
+        <v/>
+      </c>
     </row>
     <row r="510">
-      <c r="A510" t="inlineStr"/>
+      <c r="A510" t="str">
+        <v/>
+      </c>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr"/>
+      <c r="A511" t="str">
+        <v/>
+      </c>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr"/>
+      <c r="A512" t="str">
+        <v/>
+      </c>
     </row>
     <row r="513">
-      <c r="A513" t="inlineStr"/>
+      <c r="A513" t="str">
+        <v/>
+      </c>
     </row>
     <row r="514">
-      <c r="A514" t="inlineStr"/>
+      <c r="A514" t="str">
+        <v/>
+      </c>
     </row>
     <row r="515">
-      <c r="A515" t="inlineStr"/>
+      <c r="A515" t="str">
+        <v/>
+      </c>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr"/>
+      <c r="A516" t="str">
+        <v/>
+      </c>
     </row>
     <row r="517">
-      <c r="A517" t="inlineStr"/>
+      <c r="A517" t="str">
+        <v/>
+      </c>
     </row>
     <row r="518">
-      <c r="A518" t="inlineStr"/>
+      <c r="A518" t="str">
+        <v/>
+      </c>
     </row>
     <row r="519">
-      <c r="A519" t="inlineStr"/>
+      <c r="A519" t="str">
+        <v/>
+      </c>
     </row>
     <row r="520">
-      <c r="A520" t="inlineStr"/>
+      <c r="A520" t="str">
+        <v/>
+      </c>
     </row>
     <row r="521">
-      <c r="A521" t="inlineStr"/>
+      <c r="A521" t="str">
+        <v/>
+      </c>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr"/>
+      <c r="A522" t="str">
+        <v/>
+      </c>
     </row>
     <row r="523">
-      <c r="A523" t="inlineStr"/>
+      <c r="A523" t="str">
+        <v/>
+      </c>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr"/>
+      <c r="A524" t="str">
+        <v/>
+      </c>
     </row>
     <row r="525">
-      <c r="A525" t="inlineStr"/>
+      <c r="A525" t="str">
+        <v/>
+      </c>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr"/>
+      <c r="A526" t="str">
+        <v/>
+      </c>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr"/>
+      <c r="A527" t="str">
+        <v/>
+      </c>
     </row>
     <row r="528">
-      <c r="A528" t="inlineStr"/>
+      <c r="A528" t="str">
+        <v/>
+      </c>
     </row>
     <row r="529">
-      <c r="A529" t="inlineStr"/>
+      <c r="A529" t="str">
+        <v/>
+      </c>
     </row>
     <row r="530">
-      <c r="A530" t="inlineStr"/>
+      <c r="A530" t="str">
+        <v/>
+      </c>
     </row>
     <row r="531">
-      <c r="A531" t="inlineStr"/>
+      <c r="A531" t="str">
+        <v/>
+      </c>
     </row>
     <row r="532">
-      <c r="A532" t="inlineStr"/>
+      <c r="A532" t="str">
+        <v/>
+      </c>
     </row>
     <row r="533">
-      <c r="A533" t="inlineStr"/>
+      <c r="A533" t="str">
+        <v/>
+      </c>
     </row>
     <row r="534">
-      <c r="A534" t="inlineStr"/>
+      <c r="A534" t="str">
+        <v/>
+      </c>
     </row>
     <row r="535">
-      <c r="A535" t="inlineStr"/>
+      <c r="A535" t="str">
+        <v/>
+      </c>
     </row>
     <row r="536">
-      <c r="A536" t="inlineStr"/>
+      <c r="A536" t="str">
+        <v/>
+      </c>
     </row>
     <row r="537">
-      <c r="A537" t="inlineStr"/>
+      <c r="A537" t="str">
+        <v/>
+      </c>
     </row>
     <row r="538">
-      <c r="A538" t="inlineStr"/>
+      <c r="A538" t="str">
+        <v/>
+      </c>
     </row>
     <row r="539">
-      <c r="A539" t="inlineStr"/>
+      <c r="A539" t="str">
+        <v/>
+      </c>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr"/>
+      <c r="A540" t="str">
+        <v/>
+      </c>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr"/>
+      <c r="A541" t="str">
+        <v/>
+      </c>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr"/>
+      <c r="A542" t="str">
+        <v/>
+      </c>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr"/>
+      <c r="A543" t="str">
+        <v/>
+      </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr"/>
+      <c r="A544" t="str">
+        <v/>
+      </c>
     </row>
     <row r="545">
-      <c r="A545" t="inlineStr"/>
+      <c r="A545" t="str">
+        <v/>
+      </c>
     </row>
     <row r="546">
-      <c r="A546" t="inlineStr"/>
+      <c r="A546" t="str">
+        <v/>
+      </c>
     </row>
     <row r="547">
-      <c r="A547" t="inlineStr"/>
+      <c r="A547" t="str">
+        <v/>
+      </c>
     </row>
     <row r="548">
-      <c r="A548" t="inlineStr"/>
+      <c r="A548" t="str">
+        <v/>
+      </c>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr"/>
+      <c r="A549" t="str">
+        <v/>
+      </c>
     </row>
     <row r="550">
-      <c r="A550" t="inlineStr"/>
+      <c r="A550" t="str">
+        <v/>
+      </c>
     </row>
     <row r="551">
-      <c r="A551" t="inlineStr"/>
+      <c r="A551" t="str">
+        <v/>
+      </c>
     </row>
     <row r="552">
-      <c r="A552" t="inlineStr"/>
+      <c r="A552" t="str">
+        <v/>
+      </c>
     </row>
     <row r="553">
-      <c r="A553" t="inlineStr"/>
+      <c r="A553" t="str">
+        <v/>
+      </c>
     </row>
     <row r="554">
-      <c r="A554" t="inlineStr"/>
+      <c r="A554" t="str">
+        <v/>
+      </c>
     </row>
     <row r="555">
-      <c r="A555" t="inlineStr"/>
+      <c r="A555" t="str">
+        <v/>
+      </c>
     </row>
     <row r="556">
-      <c r="A556" t="inlineStr"/>
+      <c r="A556" t="str">
+        <v/>
+      </c>
     </row>
     <row r="557">
-      <c r="A557" t="inlineStr"/>
+      <c r="A557" t="str">
+        <v/>
+      </c>
     </row>
     <row r="558">
-      <c r="A558" t="inlineStr"/>
+      <c r="A558" t="str">
+        <v/>
+      </c>
     </row>
     <row r="559">
-      <c r="A559" t="inlineStr"/>
+      <c r="A559" t="str">
+        <v/>
+      </c>
     </row>
     <row r="560">
-      <c r="A560" t="inlineStr"/>
+      <c r="A560" t="str">
+        <v/>
+      </c>
     </row>
     <row r="561">
-      <c r="A561" t="inlineStr"/>
+      <c r="A561" t="str">
+        <v/>
+      </c>
     </row>
     <row r="562">
-      <c r="A562" t="inlineStr"/>
+      <c r="A562" t="str">
+        <v/>
+      </c>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr"/>
+      <c r="A563" t="str">
+        <v/>
+      </c>
     </row>
     <row r="564">
-      <c r="A564" t="inlineStr"/>
+      <c r="A564" t="str">
+        <v/>
+      </c>
     </row>
     <row r="565">
-      <c r="A565" t="inlineStr"/>
+      <c r="A565" t="str">
+        <v/>
+      </c>
     </row>
     <row r="566">
-      <c r="A566" t="inlineStr"/>
+      <c r="A566" t="str">
+        <v/>
+      </c>
     </row>
     <row r="567">
-      <c r="A567" t="inlineStr"/>
+      <c r="A567" t="str">
+        <v/>
+      </c>
     </row>
     <row r="568">
-      <c r="A568" t="inlineStr"/>
+      <c r="A568" t="str">
+        <v/>
+      </c>
     </row>
     <row r="569">
-      <c r="A569" t="inlineStr"/>
+      <c r="A569" t="str">
+        <v/>
+      </c>
     </row>
     <row r="570">
-      <c r="A570" t="inlineStr"/>
+      <c r="A570" t="str">
+        <v/>
+      </c>
     </row>
     <row r="571">
-      <c r="A571" t="inlineStr"/>
+      <c r="A571" t="str">
+        <v/>
+      </c>
     </row>
     <row r="572">
-      <c r="A572" t="inlineStr"/>
+      <c r="A572" t="str">
+        <v/>
+      </c>
     </row>
     <row r="573">
-      <c r="A573" t="inlineStr"/>
+      <c r="A573" t="str">
+        <v/>
+      </c>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr"/>
+      <c r="A574" t="str">
+        <v/>
+      </c>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr"/>
+      <c r="A575" t="str">
+        <v/>
+      </c>
     </row>
     <row r="576">
-      <c r="A576" t="inlineStr"/>
+      <c r="A576" t="str">
+        <v/>
+      </c>
     </row>
     <row r="577">
-      <c r="A577" t="inlineStr"/>
+      <c r="A577" t="str">
+        <v/>
+      </c>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr"/>
+      <c r="A578" t="str">
+        <v/>
+      </c>
     </row>
     <row r="579">
-      <c r="A579" t="inlineStr"/>
+      <c r="A579" t="str">
+        <v/>
+      </c>
     </row>
     <row r="580">
-      <c r="A580" t="inlineStr"/>
+      <c r="A580" t="str">
+        <v/>
+      </c>
     </row>
     <row r="581">
-      <c r="A581" t="inlineStr"/>
+      <c r="A581" t="str">
+        <v/>
+      </c>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr"/>
+      <c r="A582" t="str">
+        <v/>
+      </c>
     </row>
     <row r="583">
-      <c r="A583" t="inlineStr"/>
+      <c r="A583" t="str">
+        <v/>
+      </c>
     </row>
     <row r="584">
-      <c r="A584" t="inlineStr"/>
+      <c r="A584" t="str">
+        <v/>
+      </c>
     </row>
     <row r="585">
-      <c r="A585" t="inlineStr"/>
+      <c r="A585" t="str">
+        <v/>
+      </c>
     </row>
     <row r="586">
-      <c r="A586" t="inlineStr"/>
+      <c r="A586" t="str">
+        <v/>
+      </c>
     </row>
     <row r="587">
-      <c r="A587" t="inlineStr"/>
+      <c r="A587" t="str">
+        <v/>
+      </c>
     </row>
     <row r="588">
-      <c r="A588" t="inlineStr"/>
+      <c r="A588" t="str">
+        <v/>
+      </c>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr"/>
+      <c r="A589" t="str">
+        <v/>
+      </c>
     </row>
     <row r="590">
-      <c r="A590" t="inlineStr"/>
+      <c r="A590" t="str">
+        <v/>
+      </c>
     </row>
     <row r="591">
-      <c r="A591" t="inlineStr"/>
+      <c r="A591" t="str">
+        <v/>
+      </c>
     </row>
     <row r="592">
-      <c r="A592" t="inlineStr"/>
+      <c r="A592" t="str">
+        <v/>
+      </c>
     </row>
     <row r="593">
-      <c r="A593" t="inlineStr"/>
+      <c r="A593" t="str">
+        <v/>
+      </c>
     </row>
     <row r="594">
-      <c r="A594" t="inlineStr"/>
+      <c r="A594" t="str">
+        <v/>
+      </c>
     </row>
     <row r="595">
-      <c r="A595" t="inlineStr"/>
+      <c r="A595" t="str">
+        <v/>
+      </c>
     </row>
     <row r="596">
-      <c r="A596" t="inlineStr"/>
+      <c r="A596" t="str">
+        <v/>
+      </c>
     </row>
     <row r="597">
-      <c r="A597" t="inlineStr"/>
+      <c r="A597" t="str">
+        <v/>
+      </c>
     </row>
     <row r="598">
-      <c r="A598" t="inlineStr"/>
+      <c r="A598" t="str">
+        <v/>
+      </c>
     </row>
     <row r="599">
-      <c r="A599" t="inlineStr"/>
+      <c r="A599" t="str">
+        <v/>
+      </c>
     </row>
     <row r="600">
-      <c r="A600" t="inlineStr"/>
+      <c r="A600" t="str">
+        <v/>
+      </c>
     </row>
     <row r="601">
-      <c r="A601" t="inlineStr"/>
+      <c r="A601" t="str">
+        <v/>
+      </c>
     </row>
     <row r="602">
-      <c r="A602" t="inlineStr"/>
+      <c r="A602" t="str">
+        <v/>
+      </c>
     </row>
     <row r="603">
-      <c r="A603" t="inlineStr"/>
+      <c r="A603" t="str">
+        <v/>
+      </c>
     </row>
     <row r="604">
-      <c r="A604" t="inlineStr"/>
+      <c r="A604" t="str">
+        <v/>
+      </c>
     </row>
     <row r="605">
-      <c r="A605" t="inlineStr"/>
+      <c r="A605" t="str">
+        <v/>
+      </c>
     </row>
     <row r="606">
-      <c r="A606" t="inlineStr"/>
+      <c r="A606" t="str">
+        <v/>
+      </c>
     </row>
     <row r="607">
-      <c r="A607" t="inlineStr"/>
+      <c r="A607" t="str">
+        <v/>
+      </c>
     </row>
     <row r="608">
-      <c r="A608" t="inlineStr"/>
+      <c r="A608" t="str">
+        <v/>
+      </c>
     </row>
     <row r="609">
-      <c r="A609" t="inlineStr"/>
+      <c r="A609" t="str">
+        <v/>
+      </c>
     </row>
     <row r="610">
-      <c r="A610" t="inlineStr"/>
+      <c r="A610" t="str">
+        <v/>
+      </c>
     </row>
     <row r="611">
-      <c r="A611" t="inlineStr"/>
+      <c r="A611" t="str">
+        <v/>
+      </c>
     </row>
     <row r="612">
-      <c r="A612" t="inlineStr"/>
+      <c r="A612" t="str">
+        <v/>
+      </c>
     </row>
     <row r="613">
-      <c r="A613" t="inlineStr"/>
+      <c r="A613" t="str">
+        <v/>
+      </c>
     </row>
     <row r="614">
-      <c r="A614" t="inlineStr"/>
+      <c r="A614" t="str">
+        <v/>
+      </c>
     </row>
     <row r="615">
-      <c r="A615" t="inlineStr"/>
+      <c r="A615" t="str">
+        <v/>
+      </c>
     </row>
     <row r="616">
-      <c r="A616" t="inlineStr"/>
+      <c r="A616" t="str">
+        <v/>
+      </c>
     </row>
     <row r="617">
-      <c r="A617" t="inlineStr"/>
+      <c r="A617" t="str">
+        <v/>
+      </c>
     </row>
     <row r="618">
-      <c r="A618" t="inlineStr"/>
+      <c r="A618" t="str">
+        <v/>
+      </c>
     </row>
     <row r="619">
-      <c r="A619" t="inlineStr"/>
+      <c r="A619" t="str">
+        <v/>
+      </c>
     </row>
     <row r="620">
-      <c r="A620" t="inlineStr"/>
+      <c r="A620" t="str">
+        <v/>
+      </c>
     </row>
     <row r="621">
-      <c r="A621" t="inlineStr"/>
+      <c r="A621" t="str">
+        <v/>
+      </c>
     </row>
     <row r="622">
-      <c r="A622" t="inlineStr"/>
+      <c r="A622" t="str">
+        <v/>
+      </c>
     </row>
     <row r="623">
-      <c r="A623" t="inlineStr"/>
+      <c r="A623" t="str">
+        <v/>
+      </c>
     </row>
     <row r="624">
-      <c r="A624" t="inlineStr"/>
+      <c r="A624" t="str">
+        <v/>
+      </c>
     </row>
     <row r="625">
-      <c r="A625" t="inlineStr"/>
+      <c r="A625" t="str">
+        <v/>
+      </c>
     </row>
     <row r="626">
-      <c r="A626" t="inlineStr"/>
+      <c r="A626" t="str">
+        <v/>
+      </c>
     </row>
     <row r="627">
-      <c r="A627" t="inlineStr"/>
+      <c r="A627" t="str">
+        <v/>
+      </c>
     </row>
     <row r="628">
-      <c r="A628" t="inlineStr"/>
+      <c r="A628" t="str">
+        <v/>
+      </c>
     </row>
     <row r="629">
-      <c r="A629" t="inlineStr"/>
+      <c r="A629" t="str">
+        <v/>
+      </c>
     </row>
     <row r="630">
-      <c r="A630" t="inlineStr"/>
+      <c r="A630" t="str">
+        <v/>
+      </c>
     </row>
     <row r="631">
-      <c r="A631" t="inlineStr"/>
+      <c r="A631" t="str">
+        <v/>
+      </c>
     </row>
     <row r="632">
-      <c r="A632" t="inlineStr"/>
+      <c r="A632" t="str">
+        <v/>
+      </c>
     </row>
     <row r="633">
-      <c r="A633" t="inlineStr"/>
+      <c r="A633" t="str">
+        <v/>
+      </c>
     </row>
     <row r="634">
-      <c r="A634" t="inlineStr"/>
+      <c r="A634" t="str">
+        <v/>
+      </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr"/>
+      <c r="A635" t="str">
+        <v/>
+      </c>
     </row>
     <row r="636">
-      <c r="A636" t="inlineStr"/>
+      <c r="A636" t="str">
+        <v/>
+      </c>
     </row>
     <row r="637">
-      <c r="A637" t="inlineStr"/>
+      <c r="A637" t="str">
+        <v/>
+      </c>
     </row>
     <row r="638">
-      <c r="A638" t="inlineStr"/>
+      <c r="A638" t="str">
+        <v/>
+      </c>
     </row>
     <row r="639">
-      <c r="A639" t="inlineStr"/>
+      <c r="A639" t="str">
+        <v/>
+      </c>
     </row>
     <row r="640">
-      <c r="A640" t="inlineStr"/>
+      <c r="A640" t="str">
+        <v/>
+      </c>
     </row>
     <row r="641">
-      <c r="A641" t="inlineStr"/>
+      <c r="A641" t="str">
+        <v/>
+      </c>
     </row>
     <row r="642">
-      <c r="A642" t="inlineStr"/>
+      <c r="A642" t="str">
+        <v/>
+      </c>
     </row>
     <row r="643">
-      <c r="A643" t="inlineStr"/>
+      <c r="A643" t="str">
+        <v/>
+      </c>
     </row>
     <row r="644">
-      <c r="A644" t="inlineStr"/>
+      <c r="A644" t="str">
+        <v/>
+      </c>
     </row>
     <row r="645">
-      <c r="A645" t="inlineStr"/>
+      <c r="A645" t="str">
+        <v/>
+      </c>
     </row>
     <row r="646">
-      <c r="A646" t="inlineStr"/>
+      <c r="A646" t="str">
+        <v/>
+      </c>
     </row>
     <row r="647">
-      <c r="A647" t="inlineStr"/>
+      <c r="A647" t="str">
+        <v/>
+      </c>
     </row>
     <row r="648">
-      <c r="A648" t="inlineStr"/>
+      <c r="A648" t="str">
+        <v/>
+      </c>
     </row>
     <row r="649">
-      <c r="A649" t="inlineStr"/>
+      <c r="A649" t="str">
+        <v/>
+      </c>
     </row>
     <row r="650">
-      <c r="A650" t="inlineStr"/>
+      <c r="A650" t="str">
+        <v/>
+      </c>
     </row>
     <row r="651">
-      <c r="A651" t="inlineStr"/>
+      <c r="A651" t="str">
+        <v/>
+      </c>
     </row>
     <row r="652">
-      <c r="A652" t="inlineStr"/>
+      <c r="A652" t="str">
+        <v/>
+      </c>
     </row>
     <row r="653">
-      <c r="A653" t="inlineStr"/>
+      <c r="A653" t="str">
+        <v/>
+      </c>
     </row>
     <row r="654">
-      <c r="A654" t="inlineStr"/>
+      <c r="A654" t="str">
+        <v/>
+      </c>
     </row>
     <row r="655">
-      <c r="A655" t="inlineStr"/>
+      <c r="A655" t="str">
+        <v/>
+      </c>
     </row>
     <row r="656">
-      <c r="A656" t="inlineStr"/>
+      <c r="A656" t="str">
+        <v/>
+      </c>
     </row>
     <row r="657">
-      <c r="A657" t="inlineStr"/>
+      <c r="A657" t="str">
+        <v/>
+      </c>
     </row>
     <row r="658">
-      <c r="A658" t="inlineStr"/>
+      <c r="A658" t="str">
+        <v/>
+      </c>
     </row>
     <row r="659">
-      <c r="A659" t="inlineStr"/>
+      <c r="A659" t="str">
+        <v/>
+      </c>
     </row>
     <row r="660">
-      <c r="A660" t="inlineStr"/>
+      <c r="A660" t="str">
+        <v/>
+      </c>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr"/>
+      <c r="A661" t="str">
+        <v/>
+      </c>
     </row>
     <row r="662">
-      <c r="A662" t="inlineStr"/>
+      <c r="A662" t="str">
+        <v/>
+      </c>
     </row>
     <row r="663">
-      <c r="A663" t="inlineStr"/>
+      <c r="A663" t="str">
+        <v/>
+      </c>
     </row>
     <row r="664">
-      <c r="A664" t="inlineStr"/>
+      <c r="A664" t="str">
+        <v/>
+      </c>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr"/>
+      <c r="A665" t="str">
+        <v/>
+      </c>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr"/>
+      <c r="A666" t="str">
+        <v/>
+      </c>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr"/>
+      <c r="A667" t="str">
+        <v/>
+      </c>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr"/>
+      <c r="A668" t="str">
+        <v/>
+      </c>
     </row>
     <row r="669">
-      <c r="A669" t="inlineStr"/>
+      <c r="A669" t="str">
+        <v/>
+      </c>
     </row>
     <row r="670">
-      <c r="A670" t="inlineStr"/>
+      <c r="A670" t="str">
+        <v/>
+      </c>
     </row>
     <row r="671">
-      <c r="A671" t="inlineStr"/>
+      <c r="A671" t="str">
+        <v/>
+      </c>
     </row>
     <row r="672">
-      <c r="A672" t="inlineStr"/>
+      <c r="A672" t="str">
+        <v/>
+      </c>
     </row>
     <row r="673">
-      <c r="A673" t="inlineStr"/>
+      <c r="A673" t="str">
+        <v/>
+      </c>
     </row>
     <row r="674">
-      <c r="A674" t="inlineStr"/>
+      <c r="A674" t="str">
+        <v/>
+      </c>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr"/>
+      <c r="A675" t="str">
+        <v/>
+      </c>
     </row>
     <row r="676">
-      <c r="A676" t="inlineStr"/>
+      <c r="A676" t="str">
+        <v/>
+      </c>
     </row>
     <row r="677">
-      <c r="A677" t="inlineStr"/>
+      <c r="A677" t="str">
+        <v/>
+      </c>
     </row>
     <row r="678">
-      <c r="A678" t="inlineStr"/>
+      <c r="A678" t="str">
+        <v/>
+      </c>
     </row>
     <row r="679">
-      <c r="A679" t="inlineStr"/>
+      <c r="A679" t="str">
+        <v/>
+      </c>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr"/>
+      <c r="A680" t="str">
+        <v/>
+      </c>
     </row>
     <row r="681">
-      <c r="A681" t="inlineStr"/>
+      <c r="A681" t="str">
+        <v/>
+      </c>
     </row>
     <row r="682">
-      <c r="A682" t="inlineStr"/>
+      <c r="A682" t="str">
+        <v/>
+      </c>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr"/>
+      <c r="A683" t="str">
+        <v/>
+      </c>
     </row>
     <row r="684">
-      <c r="A684" t="inlineStr"/>
+      <c r="A684" t="str">
+        <v/>
+      </c>
     </row>
     <row r="685">
-      <c r="A685" t="inlineStr"/>
+      <c r="A685" t="str">
+        <v/>
+      </c>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr"/>
+      <c r="A686" t="str">
+        <v/>
+      </c>
     </row>
     <row r="687">
-      <c r="A687" t="inlineStr"/>
+      <c r="A687" t="str">
+        <v/>
+      </c>
     </row>
     <row r="688">
-      <c r="A688" t="inlineStr"/>
+      <c r="A688" t="str">
+        <v/>
+      </c>
     </row>
     <row r="689">
-      <c r="A689" t="inlineStr"/>
+      <c r="A689" t="str">
+        <v/>
+      </c>
     </row>
     <row r="690">
-      <c r="A690" t="inlineStr"/>
+      <c r="A690" t="str">
+        <v/>
+      </c>
     </row>
     <row r="691">
-      <c r="A691" t="inlineStr"/>
+      <c r="A691" t="str">
+        <v/>
+      </c>
     </row>
     <row r="692">
-      <c r="A692" t="inlineStr"/>
+      <c r="A692" t="str">
+        <v/>
+      </c>
     </row>
     <row r="693">
-      <c r="A693" t="inlineStr"/>
+      <c r="A693" t="str">
+        <v/>
+      </c>
     </row>
     <row r="694">
-      <c r="A694" t="inlineStr"/>
+      <c r="A694" t="str">
+        <v/>
+      </c>
     </row>
     <row r="695">
-      <c r="A695" t="inlineStr"/>
+      <c r="A695" t="str">
+        <v/>
+      </c>
     </row>
     <row r="696">
-      <c r="A696" t="inlineStr"/>
+      <c r="A696" t="str">
+        <v/>
+      </c>
     </row>
     <row r="697">
-      <c r="A697" t="inlineStr"/>
+      <c r="A697" t="str">
+        <v/>
+      </c>
     </row>
     <row r="698">
-      <c r="A698" t="inlineStr"/>
+      <c r="A698" t="str">
+        <v/>
+      </c>
     </row>
     <row r="699">
-      <c r="A699" t="inlineStr"/>
+      <c r="A699" t="str">
+        <v/>
+      </c>
     </row>
     <row r="700">
-      <c r="A700" t="inlineStr"/>
+      <c r="A700" t="str">
+        <v/>
+      </c>
     </row>
     <row r="701">
-      <c r="A701" t="inlineStr"/>
+      <c r="A701" t="str">
+        <v/>
+      </c>
     </row>
     <row r="702">
-      <c r="A702" t="inlineStr"/>
+      <c r="A702" t="str">
+        <v/>
+      </c>
     </row>
     <row r="703">
-      <c r="A703" t="inlineStr"/>
+      <c r="A703" t="str">
+        <v/>
+      </c>
     </row>
     <row r="704">
-      <c r="A704" t="inlineStr"/>
+      <c r="A704" t="str">
+        <v/>
+      </c>
     </row>
     <row r="705">
-      <c r="A705" t="inlineStr"/>
+      <c r="A705" t="str">
+        <v/>
+      </c>
     </row>
     <row r="706">
-      <c r="A706" t="inlineStr"/>
+      <c r="A706" t="str">
+        <v/>
+      </c>
     </row>
     <row r="707">
-      <c r="A707" t="inlineStr"/>
+      <c r="A707" t="str">
+        <v/>
+      </c>
     </row>
     <row r="708">
-      <c r="A708" t="inlineStr"/>
+      <c r="A708" t="str">
+        <v/>
+      </c>
     </row>
     <row r="709">
-      <c r="A709" t="inlineStr"/>
+      <c r="A709" t="str">
+        <v/>
+      </c>
     </row>
     <row r="710">
-      <c r="A710" t="inlineStr"/>
+      <c r="A710" t="str">
+        <v/>
+      </c>
     </row>
     <row r="711">
-      <c r="A711" t="inlineStr"/>
+      <c r="A711" t="str">
+        <v/>
+      </c>
     </row>
     <row r="712">
-      <c r="A712" t="inlineStr"/>
+      <c r="A712" t="str">
+        <v/>
+      </c>
     </row>
     <row r="713">
-      <c r="A713" t="inlineStr"/>
+      <c r="A713" t="str">
+        <v/>
+      </c>
     </row>
     <row r="714">
-      <c r="A714" t="inlineStr"/>
+      <c r="A714" t="str">
+        <v/>
+      </c>
     </row>
     <row r="715">
-      <c r="A715" t="inlineStr"/>
+      <c r="A715" t="str">
+        <v/>
+      </c>
     </row>
     <row r="716">
-      <c r="A716" t="inlineStr"/>
+      <c r="A716" t="str">
+        <v/>
+      </c>
     </row>
     <row r="717">
-      <c r="A717" t="inlineStr"/>
+      <c r="A717" t="str">
+        <v/>
+      </c>
     </row>
     <row r="718">
-      <c r="A718" t="inlineStr"/>
+      <c r="A718" t="str">
+        <v/>
+      </c>
     </row>
     <row r="719">
-      <c r="A719" t="inlineStr"/>
+      <c r="A719" t="str">
+        <v/>
+      </c>
     </row>
     <row r="720">
-      <c r="A720" t="inlineStr"/>
+      <c r="A720" t="str">
+        <v/>
+      </c>
     </row>
     <row r="721">
-      <c r="A721" t="inlineStr"/>
+      <c r="A721" t="str">
+        <v/>
+      </c>
     </row>
     <row r="722">
-      <c r="A722" t="inlineStr"/>
+      <c r="A722" t="str">
+        <v/>
+      </c>
     </row>
     <row r="723">
-      <c r="A723" t="inlineStr"/>
+      <c r="A723" t="str">
+        <v/>
+      </c>
     </row>
     <row r="724">
-      <c r="A724" t="inlineStr"/>
+      <c r="A724" t="str">
+        <v/>
+      </c>
     </row>
     <row r="725">
-      <c r="A725" t="inlineStr"/>
+      <c r="A725" t="str">
+        <v/>
+      </c>
     </row>
     <row r="726">
-      <c r="A726" t="inlineStr"/>
+      <c r="A726" t="str">
+        <v/>
+      </c>
     </row>
     <row r="727">
-      <c r="A727" t="inlineStr"/>
+      <c r="A727" t="str">
+        <v/>
+      </c>
     </row>
     <row r="728">
-      <c r="A728" t="inlineStr"/>
+      <c r="A728" t="str">
+        <v/>
+      </c>
     </row>
     <row r="729">
-      <c r="A729" t="inlineStr"/>
+      <c r="A729" t="str">
+        <v/>
+      </c>
     </row>
     <row r="730">
-      <c r="A730" t="inlineStr"/>
+      <c r="A730" t="str">
+        <v/>
+      </c>
     </row>
     <row r="731">
-      <c r="A731" t="inlineStr"/>
+      <c r="A731" t="str">
+        <v/>
+      </c>
     </row>
     <row r="732">
-      <c r="A732" t="inlineStr"/>
+      <c r="A732" t="str">
+        <v/>
+      </c>
     </row>
     <row r="733">
-      <c r="A733" t="inlineStr"/>
+      <c r="A733" t="str">
+        <v/>
+      </c>
     </row>
     <row r="734">
-      <c r="A734" t="inlineStr"/>
+      <c r="A734" t="str">
+        <v/>
+      </c>
     </row>
     <row r="735">
-      <c r="A735" t="inlineStr"/>
+      <c r="A735" t="str">
+        <v/>
+      </c>
     </row>
     <row r="736">
-      <c r="A736" t="inlineStr"/>
+      <c r="A736" t="str">
+        <v/>
+      </c>
     </row>
     <row r="737">
-      <c r="A737" t="inlineStr"/>
+      <c r="A737" t="str">
+        <v/>
+      </c>
     </row>
     <row r="738">
-      <c r="A738" t="inlineStr"/>
+      <c r="A738" t="str">
+        <v/>
+      </c>
     </row>
     <row r="739">
-      <c r="A739" t="inlineStr"/>
+      <c r="A739" t="str">
+        <v/>
+      </c>
     </row>
     <row r="740">
-      <c r="A740" t="inlineStr"/>
+      <c r="A740" t="str">
+        <v/>
+      </c>
     </row>
     <row r="741">
-      <c r="A741" t="inlineStr"/>
+      <c r="A741" t="str">
+        <v/>
+      </c>
     </row>
     <row r="742">
-      <c r="A742" t="inlineStr"/>
+      <c r="A742" t="str">
+        <v/>
+      </c>
     </row>
     <row r="743">
-      <c r="A743" t="inlineStr"/>
+      <c r="A743" t="str">
+        <v/>
+      </c>
     </row>
     <row r="744">
-      <c r="A744" t="inlineStr"/>
+      <c r="A744" t="str">
+        <v/>
+      </c>
     </row>
     <row r="745">
-      <c r="A745" t="inlineStr"/>
+      <c r="A745" t="str">
+        <v/>
+      </c>
     </row>
     <row r="746">
-      <c r="A746" t="inlineStr"/>
+      <c r="A746" t="str">
+        <v/>
+      </c>
     </row>
     <row r="747">
-      <c r="A747" t="inlineStr"/>
+      <c r="A747" t="str">
+        <v/>
+      </c>
     </row>
     <row r="748">
-      <c r="A748" t="inlineStr"/>
+      <c r="A748" t="str">
+        <v/>
+      </c>
     </row>
     <row r="749">
-      <c r="A749" t="inlineStr"/>
+      <c r="A749" t="str">
+        <v/>
+      </c>
     </row>
     <row r="750">
-      <c r="A750" t="inlineStr"/>
+      <c r="A750" t="str">
+        <v/>
+      </c>
     </row>
     <row r="751">
-      <c r="A751" t="inlineStr"/>
+      <c r="A751" t="str">
+        <v/>
+      </c>
     </row>
     <row r="752">
-      <c r="A752" t="inlineStr"/>
+      <c r="A752" t="str">
+        <v/>
+      </c>
     </row>
     <row r="753">
-      <c r="A753" t="inlineStr"/>
+      <c r="A753" t="str">
+        <v/>
+      </c>
     </row>
     <row r="754">
-      <c r="A754" t="inlineStr"/>
+      <c r="A754" t="str">
+        <v/>
+      </c>
     </row>
     <row r="755">
-      <c r="A755" t="inlineStr"/>
+      <c r="A755" t="str">
+        <v/>
+      </c>
     </row>
     <row r="756">
-      <c r="A756" t="inlineStr"/>
+      <c r="A756" t="str">
+        <v/>
+      </c>
     </row>
     <row r="757">
-      <c r="A757" t="inlineStr"/>
+      <c r="A757" t="str">
+        <v/>
+      </c>
     </row>
     <row r="758">
-      <c r="A758" t="inlineStr"/>
+      <c r="A758" t="str">
+        <v/>
+      </c>
     </row>
     <row r="759">
-      <c r="A759" t="inlineStr"/>
+      <c r="A759" t="str">
+        <v/>
+      </c>
     </row>
     <row r="760">
-      <c r="A760" t="inlineStr"/>
+      <c r="A760" t="str">
+        <v/>
+      </c>
     </row>
     <row r="761">
-      <c r="A761" t="inlineStr"/>
+      <c r="A761" t="str">
+        <v/>
+      </c>
     </row>
     <row r="762">
-      <c r="A762" t="inlineStr"/>
+      <c r="A762" t="str">
+        <v/>
+      </c>
     </row>
     <row r="763">
-      <c r="A763" t="inlineStr"/>
+      <c r="A763" t="str">
+        <v/>
+      </c>
     </row>
     <row r="764">
-      <c r="A764" t="inlineStr"/>
+      <c r="A764" t="str">
+        <v/>
+      </c>
     </row>
     <row r="765">
-      <c r="A765" t="inlineStr"/>
+      <c r="A765" t="str">
+        <v/>
+      </c>
     </row>
     <row r="766">
-      <c r="A766" t="inlineStr"/>
+      <c r="A766" t="str">
+        <v/>
+      </c>
     </row>
     <row r="767">
-      <c r="A767" t="inlineStr"/>
+      <c r="A767" t="str">
+        <v/>
+      </c>
     </row>
     <row r="768">
-      <c r="A768" t="inlineStr"/>
+      <c r="A768" t="str">
+        <v/>
+      </c>
     </row>
     <row r="769">
-      <c r="A769" t="inlineStr"/>
+      <c r="A769" t="str">
+        <v/>
+      </c>
     </row>
     <row r="770">
-      <c r="A770" t="inlineStr"/>
+      <c r="A770" t="str">
+        <v/>
+      </c>
     </row>
     <row r="771">
-      <c r="A771" t="inlineStr"/>
+      <c r="A771" t="str">
+        <v/>
+      </c>
     </row>
     <row r="772">
-      <c r="A772" t="inlineStr"/>
+      <c r="A772" t="str">
+        <v/>
+      </c>
     </row>
     <row r="773">
-      <c r="A773" t="inlineStr"/>
+      <c r="A773" t="str">
+        <v/>
+      </c>
     </row>
     <row r="774">
-      <c r="A774" t="inlineStr"/>
+      <c r="A774" t="str">
+        <v/>
+      </c>
     </row>
     <row r="775">
-      <c r="A775" t="inlineStr"/>
+      <c r="A775" t="str">
+        <v/>
+      </c>
     </row>
     <row r="776">
-      <c r="A776" t="inlineStr"/>
+      <c r="A776" t="str">
+        <v/>
+      </c>
     </row>
     <row r="777">
-      <c r="A777" t="inlineStr"/>
+      <c r="A777" t="str">
+        <v/>
+      </c>
     </row>
     <row r="778">
-      <c r="A778" t="inlineStr"/>
+      <c r="A778" t="str">
+        <v/>
+      </c>
     </row>
     <row r="779">
-      <c r="A779" t="inlineStr"/>
+      <c r="A779" t="str">
+        <v/>
+      </c>
     </row>
     <row r="780">
-      <c r="A780" t="inlineStr"/>
+      <c r="A780" t="str">
+        <v/>
+      </c>
     </row>
     <row r="781">
-      <c r="A781" t="inlineStr"/>
+      <c r="A781" t="str">
+        <v/>
+      </c>
     </row>
     <row r="782">
-      <c r="A782" t="inlineStr"/>
+      <c r="A782" t="str">
+        <v/>
+      </c>
     </row>
     <row r="783">
-      <c r="A783" t="inlineStr"/>
+      <c r="A783" t="str">
+        <v/>
+      </c>
     </row>
     <row r="784">
-      <c r="A784" t="inlineStr"/>
+      <c r="A784" t="str">
+        <v/>
+      </c>
     </row>
     <row r="785">
-      <c r="A785" t="inlineStr"/>
+      <c r="A785" t="str">
+        <v/>
+      </c>
     </row>
     <row r="786">
-      <c r="A786" t="inlineStr"/>
+      <c r="A786" t="str">
+        <v/>
+      </c>
     </row>
     <row r="787">
-      <c r="A787" t="inlineStr"/>
+      <c r="A787" t="str">
+        <v/>
+      </c>
     </row>
     <row r="788">
-      <c r="A788" t="inlineStr"/>
+      <c r="A788" t="str">
+        <v/>
+      </c>
     </row>
     <row r="789">
-      <c r="A789" t="inlineStr"/>
+      <c r="A789" t="str">
+        <v/>
+      </c>
     </row>
     <row r="790">
-      <c r="A790" t="inlineStr"/>
+      <c r="A790" t="str">
+        <v/>
+      </c>
     </row>
     <row r="791">
-      <c r="A791" t="inlineStr"/>
+      <c r="A791" t="str">
+        <v/>
+      </c>
     </row>
     <row r="792">
-      <c r="A792" t="inlineStr"/>
+      <c r="A792" t="str">
+        <v/>
+      </c>
     </row>
     <row r="793">
-      <c r="A793" t="inlineStr"/>
+      <c r="A793" t="str">
+        <v/>
+      </c>
     </row>
     <row r="794">
-      <c r="A794" t="inlineStr"/>
+      <c r="A794" t="str">
+        <v/>
+      </c>
     </row>
     <row r="795">
-      <c r="A795" t="inlineStr"/>
+      <c r="A795" t="str">
+        <v/>
+      </c>
     </row>
     <row r="796">
-      <c r="A796" t="inlineStr"/>
+      <c r="A796" t="str">
+        <v/>
+      </c>
     </row>
     <row r="797">
-      <c r="A797" t="inlineStr"/>
+      <c r="A797" t="str">
+        <v/>
+      </c>
     </row>
     <row r="798">
-      <c r="A798" t="inlineStr"/>
+      <c r="A798" t="str">
+        <v/>
+      </c>
     </row>
     <row r="799">
-      <c r="A799" t="inlineStr"/>
+      <c r="A799" t="str">
+        <v/>
+      </c>
     </row>
     <row r="800">
-      <c r="A800" t="inlineStr"/>
+      <c r="A800" t="str">
+        <v/>
+      </c>
     </row>
     <row r="801">
-      <c r="A801" t="inlineStr"/>
+      <c r="A801" t="str">
+        <v/>
+      </c>
     </row>
     <row r="802">
-      <c r="A802" t="inlineStr"/>
+      <c r="A802" t="str">
+        <v/>
+      </c>
     </row>
     <row r="803">
-      <c r="A803" t="inlineStr"/>
+      <c r="A803" t="str">
+        <v/>
+      </c>
     </row>
     <row r="804">
-      <c r="A804" t="inlineStr"/>
+      <c r="A804" t="str">
+        <v/>
+      </c>
     </row>
     <row r="805">
-      <c r="A805" t="inlineStr"/>
+      <c r="A805" t="str">
+        <v/>
+      </c>
     </row>
     <row r="806">
-      <c r="A806" t="inlineStr"/>
+      <c r="A806" t="str">
+        <v/>
+      </c>
     </row>
     <row r="807">
-      <c r="A807" t="inlineStr"/>
+      <c r="A807" t="str">
+        <v/>
+      </c>
     </row>
     <row r="808">
-      <c r="A808" t="inlineStr"/>
+      <c r="A808" t="str">
+        <v/>
+      </c>
     </row>
     <row r="809">
-      <c r="A809" t="inlineStr"/>
+      <c r="A809" t="str">
+        <v/>
+      </c>
     </row>
     <row r="810">
-      <c r="A810" t="inlineStr"/>
+      <c r="A810" t="str">
+        <v/>
+      </c>
     </row>
     <row r="811">
-      <c r="A811" t="inlineStr"/>
+      <c r="A811" t="str">
+        <v/>
+      </c>
     </row>
     <row r="812">
-      <c r="A812" t="inlineStr"/>
+      <c r="A812" t="str">
+        <v/>
+      </c>
     </row>
     <row r="813">
-      <c r="A813" t="inlineStr"/>
+      <c r="A813" t="str">
+        <v/>
+      </c>
     </row>
     <row r="814">
-      <c r="A814" t="inlineStr"/>
+      <c r="A814" t="str">
+        <v/>
+      </c>
     </row>
     <row r="815">
-      <c r="A815" t="inlineStr"/>
+      <c r="A815" t="str">
+        <v/>
+      </c>
     </row>
     <row r="816">
-      <c r="A816" t="inlineStr"/>
+      <c r="A816" t="str">
+        <v/>
+      </c>
     </row>
     <row r="817">
-      <c r="A817" t="inlineStr"/>
+      <c r="A817" t="str">
+        <v/>
+      </c>
     </row>
     <row r="818">
-      <c r="A818" t="inlineStr"/>
+      <c r="A818" t="str">
+        <v/>
+      </c>
     </row>
     <row r="819">
-      <c r="A819" t="inlineStr"/>
+      <c r="A819" t="str">
+        <v/>
+      </c>
     </row>
     <row r="820">
-      <c r="A820" t="inlineStr"/>
+      <c r="A820" t="str">
+        <v/>
+      </c>
     </row>
     <row r="821">
-      <c r="A821" t="inlineStr"/>
+      <c r="A821" t="str">
+        <v/>
+      </c>
     </row>
     <row r="822">
-      <c r="A822" t="inlineStr"/>
+      <c r="A822" t="str">
+        <v/>
+      </c>
     </row>
     <row r="823">
-      <c r="A823" t="inlineStr"/>
+      <c r="A823" t="str">
+        <v/>
+      </c>
     </row>
     <row r="824">
-      <c r="A824" t="inlineStr"/>
+      <c r="A824" t="str">
+        <v/>
+      </c>
     </row>
     <row r="825">
-      <c r="A825" t="inlineStr"/>
+      <c r="A825" t="str">
+        <v/>
+      </c>
     </row>
     <row r="826">
-      <c r="A826" t="inlineStr"/>
+      <c r="A826" t="str">
+        <v/>
+      </c>
     </row>
     <row r="827">
-      <c r="A827" t="inlineStr"/>
+      <c r="A827" t="str">
+        <v/>
+      </c>
     </row>
     <row r="828">
-      <c r="A828" t="inlineStr"/>
+      <c r="A828" t="str">
+        <v/>
+      </c>
     </row>
     <row r="829">
-      <c r="A829" t="inlineStr"/>
+      <c r="A829" t="str">
+        <v/>
+      </c>
     </row>
     <row r="830">
-      <c r="A830" t="inlineStr"/>
+      <c r="A830" t="str">
+        <v/>
+      </c>
     </row>
     <row r="831">
-      <c r="A831" t="inlineStr"/>
+      <c r="A831" t="str">
+        <v/>
+      </c>
     </row>
     <row r="832">
-      <c r="A832" t="inlineStr"/>
+      <c r="A832" t="str">
+        <v/>
+      </c>
     </row>
     <row r="833">
-      <c r="A833" t="inlineStr"/>
+      <c r="A833" t="str">
+        <v/>
+      </c>
     </row>
     <row r="834">
-      <c r="A834" t="inlineStr"/>
+      <c r="A834" t="str">
+        <v/>
+      </c>
     </row>
     <row r="835">
-      <c r="A835" t="inlineStr"/>
+      <c r="A835" t="str">
+        <v/>
+      </c>
     </row>
     <row r="836">
-      <c r="A836" t="inlineStr"/>
+      <c r="A836" t="str">
+        <v/>
+      </c>
     </row>
     <row r="837">
-      <c r="A837" t="inlineStr"/>
+      <c r="A837" t="str">
+        <v/>
+      </c>
     </row>
     <row r="838">
-      <c r="A838" t="inlineStr"/>
+      <c r="A838" t="str">
+        <v/>
+      </c>
     </row>
     <row r="839">
-      <c r="A839" t="inlineStr"/>
+      <c r="A839" t="str">
+        <v/>
+      </c>
     </row>
     <row r="840">
-      <c r="A840" t="inlineStr"/>
+      <c r="A840" t="str">
+        <v/>
+      </c>
     </row>
     <row r="841">
-      <c r="A841" t="inlineStr"/>
+      <c r="A841" t="str">
+        <v/>
+      </c>
     </row>
     <row r="842">
-      <c r="A842" t="inlineStr"/>
+      <c r="A842" t="str">
+        <v/>
+      </c>
     </row>
     <row r="843">
-      <c r="A843" t="inlineStr"/>
+      <c r="A843" t="str">
+        <v/>
+      </c>
     </row>
     <row r="844">
-      <c r="A844" t="inlineStr"/>
+      <c r="A844" t="str">
+        <v/>
+      </c>
     </row>
     <row r="845">
-      <c r="A845" t="inlineStr"/>
+      <c r="A845" t="str">
+        <v/>
+      </c>
     </row>
     <row r="846">
-      <c r="A846" t="inlineStr"/>
+      <c r="A846" t="str">
+        <v/>
+      </c>
     </row>
     <row r="847">
-      <c r="A847" t="inlineStr"/>
+      <c r="A847" t="str">
+        <v/>
+      </c>
     </row>
     <row r="848">
-      <c r="A848" t="inlineStr"/>
+      <c r="A848" t="str">
+        <v/>
+      </c>
     </row>
     <row r="849">
-      <c r="A849" t="inlineStr"/>
+      <c r="A849" t="str">
+        <v/>
+      </c>
     </row>
     <row r="850">
-      <c r="A850" t="inlineStr"/>
+      <c r="A850" t="str">
+        <v/>
+      </c>
     </row>
     <row r="851">
-      <c r="A851" t="inlineStr"/>
+      <c r="A851" t="str">
+        <v/>
+      </c>
     </row>
     <row r="852">
-      <c r="A852" t="inlineStr"/>
+      <c r="A852" t="str">
+        <v/>
+      </c>
     </row>
     <row r="853">
-      <c r="A853" t="inlineStr"/>
+      <c r="A853" t="str">
+        <v/>
+      </c>
     </row>
     <row r="854">
-      <c r="A854" t="inlineStr"/>
+      <c r="A854" t="str">
+        <v/>
+      </c>
     </row>
     <row r="855">
-      <c r="A855" t="inlineStr"/>
+      <c r="A855" t="str">
+        <v/>
+      </c>
     </row>
     <row r="856">
-      <c r="A856" t="inlineStr"/>
+      <c r="A856" t="str">
+        <v/>
+      </c>
     </row>
     <row r="857">
-      <c r="A857" t="inlineStr"/>
+      <c r="A857" t="str">
+        <v/>
+      </c>
     </row>
     <row r="858">
-      <c r="A858" t="inlineStr"/>
+      <c r="A858" t="str">
+        <v/>
+      </c>
     </row>
     <row r="859">
-      <c r="A859" t="inlineStr"/>
+      <c r="A859" t="str">
+        <v/>
+      </c>
     </row>
     <row r="860">
-      <c r="A860" t="inlineStr"/>
+      <c r="A860" t="str">
+        <v/>
+      </c>
     </row>
     <row r="861">
-      <c r="A861" t="inlineStr"/>
+      <c r="A861" t="str">
+        <v/>
+      </c>
     </row>
     <row r="862">
-      <c r="A862" t="inlineStr"/>
+      <c r="A862" t="str">
+        <v/>
+      </c>
     </row>
     <row r="863">
-      <c r="A863" t="inlineStr"/>
+      <c r="A863" t="str">
+        <v/>
+      </c>
     </row>
     <row r="864">
-      <c r="A864" t="inlineStr"/>
+      <c r="A864" t="str">
+        <v/>
+      </c>
     </row>
     <row r="865">
-      <c r="A865" t="inlineStr"/>
+      <c r="A865" t="str">
+        <v/>
+      </c>
     </row>
     <row r="866">
-      <c r="A866" t="inlineStr"/>
+      <c r="A866" t="str">
+        <v/>
+      </c>
     </row>
     <row r="867">
-      <c r="A867" t="inlineStr"/>
+      <c r="A867" t="str">
+        <v/>
+      </c>
     </row>
     <row r="868">
-      <c r="A868" t="inlineStr"/>
+      <c r="A868" t="str">
+        <v/>
+      </c>
     </row>
     <row r="869">
-      <c r="A869" t="inlineStr"/>
+      <c r="A869" t="str">
+        <v/>
+      </c>
     </row>
     <row r="870">
-      <c r="A870" t="inlineStr"/>
+      <c r="A870" t="str">
+        <v/>
+      </c>
     </row>
     <row r="871">
-      <c r="A871" t="inlineStr"/>
+      <c r="A871" t="str">
+        <v/>
+      </c>
     </row>
     <row r="872">
-      <c r="A872" t="inlineStr"/>
+      <c r="A872" t="str">
+        <v/>
+      </c>
     </row>
     <row r="873">
-      <c r="A873" t="inlineStr"/>
+      <c r="A873" t="str">
+        <v/>
+      </c>
     </row>
     <row r="874">
-      <c r="A874" t="inlineStr"/>
+      <c r="A874" t="str">
+        <v/>
+      </c>
     </row>
     <row r="875">
-      <c r="A875" t="inlineStr"/>
+      <c r="A875" t="str">
+        <v/>
+      </c>
     </row>
     <row r="876">
-      <c r="A876" t="inlineStr"/>
+      <c r="A876" t="str">
+        <v/>
+      </c>
     </row>
     <row r="877">
-      <c r="A877" t="inlineStr"/>
+      <c r="A877" t="str">
+        <v/>
+      </c>
     </row>
     <row r="878">
-      <c r="A878" t="inlineStr"/>
+      <c r="A878" t="str">
+        <v/>
+      </c>
     </row>
     <row r="879">
-      <c r="A879" t="inlineStr"/>
+      <c r="A879" t="str">
+        <v/>
+      </c>
     </row>
     <row r="880">
-      <c r="A880" t="inlineStr"/>
+      <c r="A880" t="str">
+        <v/>
+      </c>
     </row>
     <row r="881">
-      <c r="A881" t="inlineStr"/>
+      <c r="A881" t="str">
+        <v/>
+      </c>
     </row>
     <row r="882">
-      <c r="A882" t="inlineStr"/>
+      <c r="A882" t="str">
+        <v/>
+      </c>
     </row>
     <row r="883">
-      <c r="A883" t="inlineStr"/>
+      <c r="A883" t="str">
+        <v/>
+      </c>
     </row>
     <row r="884">
-      <c r="A884" t="inlineStr"/>
+      <c r="A884" t="str">
+        <v/>
+      </c>
     </row>
     <row r="885">
-      <c r="A885" t="inlineStr"/>
+      <c r="A885" t="str">
+        <v/>
+      </c>
     </row>
     <row r="886">
-      <c r="A886" t="inlineStr"/>
+      <c r="A886" t="str">
+        <v/>
+      </c>
     </row>
     <row r="887">
-      <c r="A887" t="inlineStr"/>
+      <c r="A887" t="str">
+        <v/>
+      </c>
     </row>
     <row r="888">
-      <c r="A888" t="inlineStr"/>
+      <c r="A888" t="str">
+        <v/>
+      </c>
     </row>
     <row r="889">
-      <c r="A889" t="inlineStr"/>
+      <c r="A889" t="str">
+        <v/>
+      </c>
     </row>
     <row r="890">
-      <c r="A890" t="inlineStr"/>
+      <c r="A890" t="str">
+        <v/>
+      </c>
     </row>
     <row r="891">
-      <c r="A891" t="inlineStr"/>
+      <c r="A891" t="str">
+        <v/>
+      </c>
     </row>
     <row r="892">
-      <c r="A892" t="inlineStr"/>
+      <c r="A892" t="str">
+        <v/>
+      </c>
     </row>
     <row r="893">
-      <c r="A893" t="inlineStr"/>
+      <c r="A893" t="str">
+        <v/>
+      </c>
     </row>
     <row r="894">
-      <c r="A894" t="inlineStr"/>
+      <c r="A894" t="str">
+        <v/>
+      </c>
     </row>
     <row r="895">
-      <c r="A895" t="inlineStr"/>
+      <c r="A895" t="str">
+        <v/>
+      </c>
     </row>
     <row r="896">
-      <c r="A896" t="inlineStr"/>
+      <c r="A896" t="str">
+        <v/>
+      </c>
     </row>
     <row r="897">
-      <c r="A897" t="inlineStr"/>
+      <c r="A897" t="str">
+        <v/>
+      </c>
     </row>
     <row r="898">
-      <c r="A898" t="inlineStr"/>
+      <c r="A898" t="str">
+        <v/>
+      </c>
     </row>
     <row r="899">
-      <c r="A899" t="inlineStr"/>
+      <c r="A899" t="str">
+        <v/>
+      </c>
     </row>
     <row r="900">
-      <c r="A900" t="inlineStr"/>
+      <c r="A900" t="str">
+        <v/>
+      </c>
     </row>
     <row r="901">
-      <c r="A901" t="inlineStr"/>
+      <c r="A901" t="str">
+        <v/>
+      </c>
     </row>
     <row r="902">
-      <c r="A902" t="inlineStr"/>
+      <c r="A902" t="str">
+        <v/>
+      </c>
     </row>
     <row r="903">
-      <c r="A903" t="inlineStr"/>
+      <c r="A903" t="str">
+        <v/>
+      </c>
     </row>
     <row r="904">
-      <c r="A904" t="inlineStr"/>
+      <c r="A904" t="str">
+        <v/>
+      </c>
     </row>
     <row r="905">
-      <c r="A905" t="inlineStr"/>
+      <c r="A905" t="str">
+        <v/>
+      </c>
     </row>
     <row r="906">
-      <c r="A906" t="inlineStr"/>
+      <c r="A906" t="str">
+        <v/>
+      </c>
     </row>
     <row r="907">
-      <c r="A907" t="inlineStr"/>
+      <c r="A907" t="str">
+        <v/>
+      </c>
     </row>
     <row r="908">
-      <c r="A908" t="inlineStr"/>
+      <c r="A908" t="str">
+        <v/>
+      </c>
     </row>
     <row r="909">
-      <c r="A909" t="inlineStr"/>
+      <c r="A909" t="str">
+        <v/>
+      </c>
     </row>
     <row r="910">
-      <c r="A910" t="inlineStr"/>
+      <c r="A910" t="str">
+        <v/>
+      </c>
     </row>
     <row r="911">
-      <c r="A911" t="inlineStr"/>
+      <c r="A911" t="str">
+        <v/>
+      </c>
     </row>
     <row r="912">
-      <c r="A912" t="inlineStr"/>
+      <c r="A912" t="str">
+        <v/>
+      </c>
     </row>
     <row r="913">
-      <c r="A913" t="inlineStr"/>
+      <c r="A913" t="str">
+        <v/>
+      </c>
     </row>
     <row r="914">
-      <c r="A914" t="inlineStr"/>
+      <c r="A914" t="str">
+        <v/>
+      </c>
     </row>
     <row r="915">
-      <c r="A915" t="inlineStr"/>
+      <c r="A915" t="str">
+        <v/>
+      </c>
     </row>
     <row r="916">
-      <c r="A916" t="inlineStr"/>
+      <c r="A916" t="str">
+        <v/>
+      </c>
     </row>
     <row r="917">
-      <c r="A917" t="inlineStr"/>
+      <c r="A917" t="str">
+        <v/>
+      </c>
     </row>
     <row r="918">
-      <c r="A918" t="inlineStr"/>
+      <c r="A918" t="str">
+        <v/>
+      </c>
     </row>
     <row r="919">
-      <c r="A919" t="inlineStr"/>
+      <c r="A919" t="str">
+        <v/>
+      </c>
     </row>
     <row r="920">
-      <c r="A920" t="inlineStr"/>
+      <c r="A920" t="str">
+        <v/>
+      </c>
     </row>
     <row r="921">
-      <c r="A921" t="inlineStr"/>
+      <c r="A921" t="str">
+        <v/>
+      </c>
     </row>
     <row r="922">
-      <c r="A922" t="inlineStr"/>
+      <c r="A922" t="str">
+        <v/>
+      </c>
     </row>
     <row r="923">
-      <c r="A923" t="inlineStr"/>
+      <c r="A923" t="str">
+        <v/>
+      </c>
     </row>
     <row r="924">
-      <c r="A924" t="inlineStr"/>
+      <c r="A924" t="str">
+        <v/>
+      </c>
     </row>
     <row r="925">
-      <c r="A925" t="inlineStr"/>
+      <c r="A925" t="str">
+        <v/>
+      </c>
     </row>
     <row r="926">
-      <c r="A926" t="inlineStr"/>
+      <c r="A926" t="str">
+        <v/>
+      </c>
     </row>
     <row r="927">
-      <c r="A927" t="inlineStr"/>
+      <c r="A927" t="str">
+        <v/>
+      </c>
     </row>
     <row r="928">
-      <c r="A928" t="inlineStr"/>
+      <c r="A928" t="str">
+        <v/>
+      </c>
     </row>
     <row r="929">
-      <c r="A929" t="inlineStr"/>
+      <c r="A929" t="str">
+        <v/>
+      </c>
     </row>
     <row r="930">
-      <c r="A930" t="inlineStr"/>
+      <c r="A930" t="str">
+        <v/>
+      </c>
     </row>
     <row r="931">
-      <c r="A931" t="inlineStr"/>
+      <c r="A931" t="str">
+        <v/>
+      </c>
     </row>
     <row r="932">
-      <c r="A932" t="inlineStr"/>
+      <c r="A932" t="str">
+        <v/>
+      </c>
     </row>
     <row r="933">
-      <c r="A933" t="inlineStr"/>
+      <c r="A933" t="str">
+        <v/>
+      </c>
     </row>
     <row r="934">
-      <c r="A934" t="inlineStr"/>
+      <c r="A934" t="str">
+        <v/>
+      </c>
     </row>
     <row r="935">
-      <c r="A935" t="inlineStr"/>
+      <c r="A935" t="str">
+        <v/>
+      </c>
     </row>
     <row r="936">
-      <c r="A936" t="inlineStr"/>
+      <c r="A936" t="str">
+        <v/>
+      </c>
     </row>
     <row r="937">
-      <c r="A937" t="inlineStr"/>
+      <c r="A937" t="str">
+        <v/>
+      </c>
     </row>
     <row r="938">
-      <c r="A938" t="inlineStr"/>
+      <c r="A938" t="str">
+        <v/>
+      </c>
     </row>
     <row r="939">
-      <c r="A939" t="inlineStr"/>
+      <c r="A939" t="str">
+        <v/>
+      </c>
     </row>
     <row r="940">
-      <c r="A940" t="inlineStr"/>
+      <c r="A940" t="str">
+        <v/>
+      </c>
     </row>
     <row r="941">
-      <c r="A941" t="inlineStr"/>
+      <c r="A941" t="str">
+        <v/>
+      </c>
     </row>
     <row r="942">
-      <c r="A942" t="inlineStr"/>
+      <c r="A942" t="str">
+        <v/>
+      </c>
     </row>
     <row r="943">
-      <c r="A943" t="inlineStr"/>
+      <c r="A943" t="str">
+        <v/>
+      </c>
     </row>
     <row r="944">
-      <c r="A944" t="inlineStr"/>
+      <c r="A944" t="str">
+        <v/>
+      </c>
     </row>
     <row r="945">
-      <c r="A945" t="inlineStr"/>
+      <c r="A945" t="str">
+        <v/>
+      </c>
     </row>
     <row r="946">
-      <c r="A946" t="inlineStr"/>
+      <c r="A946" t="str">
+        <v/>
+      </c>
     </row>
     <row r="947">
-      <c r="A947" t="inlineStr"/>
+      <c r="A947" t="str">
+        <v/>
+      </c>
     </row>
     <row r="948">
-      <c r="A948" t="inlineStr"/>
+      <c r="A948" t="str">
+        <v/>
+      </c>
     </row>
     <row r="949">
-      <c r="A949" t="inlineStr"/>
+      <c r="A949" t="str">
+        <v/>
+      </c>
     </row>
     <row r="950">
-      <c r="A950" t="inlineStr"/>
+      <c r="A950" t="str">
+        <v/>
+      </c>
     </row>
     <row r="951">
-      <c r="A951" t="inlineStr"/>
+      <c r="A951" t="str">
+        <v/>
+      </c>
     </row>
     <row r="952">
-      <c r="A952" t="inlineStr"/>
+      <c r="A952" t="str">
+        <v/>
+      </c>
     </row>
     <row r="953">
-      <c r="A953" t="inlineStr"/>
+      <c r="A953" t="str">
+        <v/>
+      </c>
     </row>
     <row r="954">
-      <c r="A954" t="inlineStr"/>
+      <c r="A954" t="str">
+        <v/>
+      </c>
     </row>
     <row r="955">
-      <c r="A955" t="inlineStr"/>
+      <c r="A955" t="str">
+        <v/>
+      </c>
     </row>
     <row r="956">
-      <c r="A956" t="inlineStr"/>
+      <c r="A956" t="str">
+        <v/>
+      </c>
     </row>
     <row r="957">
-      <c r="A957" t="inlineStr"/>
+      <c r="A957" t="str">
+        <v/>
+      </c>
     </row>
     <row r="958">
-      <c r="A958" t="inlineStr"/>
+      <c r="A958" t="str">
+        <v/>
+      </c>
     </row>
     <row r="959">
-      <c r="A959" t="inlineStr"/>
+      <c r="A959" t="str">
+        <v/>
+      </c>
     </row>
     <row r="960">
-      <c r="A960" t="inlineStr"/>
+      <c r="A960" t="str">
+        <v/>
+      </c>
     </row>
     <row r="961">
-      <c r="A961" t="inlineStr"/>
+      <c r="A961" t="str">
+        <v/>
+      </c>
     </row>
     <row r="962">
-      <c r="A962" t="inlineStr"/>
+      <c r="A962" t="str">
+        <v/>
+      </c>
     </row>
     <row r="963">
-      <c r="A963" t="inlineStr"/>
+      <c r="A963" t="str">
+        <v/>
+      </c>
     </row>
     <row r="964">
-      <c r="A964" t="inlineStr"/>
+      <c r="A964" t="str">
+        <v/>
+      </c>
     </row>
     <row r="965">
-      <c r="A965" t="inlineStr"/>
+      <c r="A965" t="str">
+        <v/>
+      </c>
     </row>
     <row r="966">
-      <c r="A966" t="inlineStr"/>
+      <c r="A966" t="str">
+        <v/>
+      </c>
     </row>
     <row r="967">
-      <c r="A967" t="inlineStr"/>
+      <c r="A967" t="str">
+        <v/>
+      </c>
     </row>
     <row r="968">
-      <c r="A968" t="inlineStr"/>
+      <c r="A968" t="str">
+        <v/>
+      </c>
     </row>
     <row r="969">
-      <c r="A969" t="inlineStr"/>
+      <c r="A969" t="str">
+        <v/>
+      </c>
     </row>
     <row r="970">
-      <c r="A970" t="inlineStr"/>
+      <c r="A970" t="str">
+        <v/>
+      </c>
     </row>
     <row r="971">
-      <c r="A971" t="inlineStr"/>
+      <c r="A971" t="str">
+        <v/>
+      </c>
     </row>
     <row r="972">
-      <c r="A972" t="inlineStr"/>
+      <c r="A972" t="str">
+        <v/>
+      </c>
     </row>
     <row r="973">
-      <c r="A973" t="inlineStr"/>
+      <c r="A973" t="str">
+        <v/>
+      </c>
     </row>
     <row r="974">
-      <c r="A974" t="inlineStr"/>
+      <c r="A974" t="str">
+        <v/>
+      </c>
     </row>
     <row r="975">
-      <c r="A975" t="inlineStr"/>
+      <c r="A975" t="str">
+        <v/>
+      </c>
     </row>
     <row r="976">
-      <c r="A976" t="inlineStr"/>
+      <c r="A976" t="str">
+        <v/>
+      </c>
     </row>
     <row r="977">
-      <c r="A977" t="inlineStr"/>
+      <c r="A977" t="str">
+        <v/>
+      </c>
     </row>
     <row r="978">
-      <c r="A978" t="inlineStr"/>
+      <c r="A978" t="str">
+        <v/>
+      </c>
     </row>
     <row r="979">
-      <c r="A979" t="inlineStr"/>
+      <c r="A979" t="str">
+        <v/>
+      </c>
     </row>
     <row r="980">
-      <c r="A980" t="inlineStr"/>
+      <c r="A980" t="str">
+        <v/>
+      </c>
     </row>
     <row r="981">
-      <c r="A981" t="inlineStr"/>
+      <c r="A981" t="str">
+        <v/>
+      </c>
     </row>
     <row r="982">
-      <c r="A982" t="inlineStr"/>
+      <c r="A982" t="str">
+        <v/>
+      </c>
     </row>
     <row r="983">
-      <c r="A983" t="inlineStr"/>
+      <c r="A983" t="str">
+        <v/>
+      </c>
     </row>
     <row r="984">
-      <c r="A984" t="inlineStr"/>
+      <c r="A984" t="str">
+        <v/>
+      </c>
     </row>
     <row r="985">
-      <c r="A985" t="inlineStr"/>
+      <c r="A985" t="str">
+        <v/>
+      </c>
     </row>
     <row r="986">
-      <c r="A986" t="inlineStr"/>
+      <c r="A986" t="str">
+        <v/>
+      </c>
     </row>
     <row r="987">
-      <c r="A987" t="inlineStr"/>
+      <c r="A987" t="str">
+        <v/>
+      </c>
     </row>
     <row r="988">
-      <c r="A988" t="inlineStr"/>
+      <c r="A988" t="str">
+        <v/>
+      </c>
     </row>
     <row r="989">
-      <c r="A989" t="inlineStr"/>
+      <c r="A989" t="str">
+        <v/>
+      </c>
     </row>
     <row r="990">
-      <c r="A990" t="inlineStr"/>
+      <c r="A990" t="str">
+        <v/>
+      </c>
     </row>
     <row r="991">
-      <c r="A991" t="inlineStr"/>
+      <c r="A991" t="str">
+        <v/>
+      </c>
     </row>
     <row r="992">
-      <c r="A992" t="inlineStr"/>
+      <c r="A992" t="str">
+        <v>AGRO.BA</v>
+      </c>
     </row>
     <row r="993">
-      <c r="A993" t="inlineStr">
-        <is>
-          <t>AGRO.BA</t>
-        </is>
+      <c r="A993" t="str">
+        <v>SEMI.BA</v>
       </c>
     </row>
     <row r="994">
-      <c r="A994" t="inlineStr">
-        <is>
-          <t>SEMI.BA</t>
-        </is>
+      <c r="A994" t="str">
+        <v>EWY</v>
       </c>
     </row>
     <row r="995">
-      <c r="A995" t="inlineStr">
-        <is>
-          <t>EWY</t>
-        </is>
-      </c>
-    </row>
-    <row r="996">
-      <c r="A996" t="inlineStr">
-        <is>
-          <t>SPCX</t>
-        </is>
+      <c r="A995" t="str">
+        <v>SPCX</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A995"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A995"/>
+  <dimension ref="A1:A994"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2076,457 +2076,457 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>TRVV</v>
+        <v>TSMC</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>TSMC</v>
+        <v>TTM</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>TTM</v>
+        <v>TV</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>TV</v>
+        <v>TWTR</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>TWTR</v>
+        <v>TXR</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>TXR</v>
+        <v>VALO</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>VALO</v>
+        <v>WBA</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>WBA</v>
+        <v>WBO</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>WBO</v>
+        <v>XROX</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>XROX</v>
+        <v>YPFD</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>YPFD</v>
+        <v>YZCA</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>YZCA</v>
+        <v>EQNR</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>EQNR</v>
+        <v>ARM</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>ARM</v>
+        <v>BKR</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>BKR</v>
+        <v>DHR</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>DHR</v>
+        <v>GT</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>GT</v>
+        <v>ISRG</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>ISRG</v>
+        <v>LAAC</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>LAAC</v>
+        <v>NXE</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>NXE</v>
+        <v>ORLY</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>ORLY</v>
+        <v>TJX</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>TJX</v>
+        <v>SAMI</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>SAMI</v>
+        <v>BHIP</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>BHIP</v>
+        <v>SEMI</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>SEMI</v>
+        <v>FERR</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>FERR</v>
+        <v>AGRO</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>AGRO</v>
+        <v>IRS</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>IRS</v>
+        <v>AL 30</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>AL 30</v>
+        <v>GD 30</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>GD 30</v>
+        <v>AL 29</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>AL 29</v>
+        <v>GD29</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>GD29</v>
+        <v>CECO2</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>CECO2</v>
+        <v>ETHA</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>ETHA</v>
+        <v>IBIT</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>IBIT</v>
+        <v>LAC</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>LAC</v>
+        <v>DIVIDENDOS</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>DIVIDENDOS</v>
+        <v>PNZIF</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>PNZIF</v>
+        <v>ASML</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>ASML</v>
+        <v>TEAM</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>TEAM</v>
+        <v>AI</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>AI</v>
+        <v>CLS</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>CLS</v>
+        <v>CEG</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>CEG</v>
+        <v>DECK</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>DECK</v>
+        <v>RGTI</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>RGTI</v>
+        <v>NOW</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>NOW</v>
+        <v>TEM</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>TEM</v>
+        <v>PATH</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>PATH</v>
+        <v>VRTX</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>VRTX</v>
+        <v>VST</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>VST</v>
+        <v>USO</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>USO</v>
+        <v>EFA</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>EFA</v>
+        <v>IEMG</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>IEMG</v>
+        <v>ACWI</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>ACWI</v>
+        <v>GDX</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>GDX</v>
+        <v>HOOD</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>HOOD</v>
+        <v>CRWV</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>CRWV</v>
+        <v>OKLO</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>OKLO</v>
+        <v>RKLB</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>RKLB</v>
+        <v>ALAB</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ALAB</v>
+        <v>ASTS</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>ASTS</v>
+        <v>IREN</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>IREN</v>
+        <v>ECL</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ECL</v>
+        <v>SPHQ</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>SPHQ</v>
+        <v>EFECTIVO</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>EFECTIVO</v>
+        <v>URA</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>URA</v>
+        <v>COPX</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>COPX</v>
+        <v>ILF</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>ILF</v>
+        <v>ESGU</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>ESGU</v>
+        <v>IVV</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>IVV</v>
+        <v>BMNR</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>BMNR</v>
+        <v>BX</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>BX</v>
+        <v>RSP</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>RSP</v>
+        <v>EWI</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>EWI</v>
+        <v>XME</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>XME</v>
+        <v>ICLN</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>ICLN</v>
+        <v>CRWD</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>CRWD</v>
+        <v>ANET</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>ANET</v>
+        <v>O</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>O</v>
+        <v>GLNG</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>GLNG</v>
+        <v>SNDK</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>SNDK</v>
+        <v>NBIS</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>NBIS</v>
+        <v>HIMS</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>HIMS</v>
+        <v>ONDS</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ONDS</v>
+        <v>COP</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>COP</v>
+        <v>NEE</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>NEE</v>
+        <v>MP</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>MP</v>
+        <v>CCJ</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>CCJ</v>
+        <v>FISV</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>FISV</v>
+        <v>KEEL</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>KEEL</v>
+        <v>NVO</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>NVO</v>
+        <v/>
       </c>
     </row>
     <row r="427">
@@ -5351,32 +5351,27 @@
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v/>
+        <v>AGRO.BA</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>AGRO.BA</v>
+        <v>SEMI.BA</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>SEMI.BA</v>
+        <v>EWY</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>EWY</v>
-      </c>
-    </row>
-    <row r="995">
-      <c r="A995" t="str">
         <v>SPCX</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A995"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A994"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A994"/>
+  <dimension ref="A1:A993"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2081,447 +2081,447 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>TTM</v>
+        <v>TV</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>TV</v>
+        <v>TWTR</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>TWTR</v>
+        <v>TXR</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>TXR</v>
+        <v>VALO</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>VALO</v>
+        <v>WBA</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>WBA</v>
+        <v>WBO</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>WBO</v>
+        <v>XROX</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>XROX</v>
+        <v>YPFD</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>YPFD</v>
+        <v>YZCA</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>YZCA</v>
+        <v>EQNR</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>EQNR</v>
+        <v>ARM</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>ARM</v>
+        <v>BKR</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>BKR</v>
+        <v>DHR</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>DHR</v>
+        <v>GT</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>GT</v>
+        <v>ISRG</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>ISRG</v>
+        <v>LAAC</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>LAAC</v>
+        <v>NXE</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>NXE</v>
+        <v>ORLY</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>ORLY</v>
+        <v>TJX</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>TJX</v>
+        <v>SAMI</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>SAMI</v>
+        <v>BHIP</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>BHIP</v>
+        <v>SEMI</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>SEMI</v>
+        <v>FERR</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>FERR</v>
+        <v>AGRO</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>AGRO</v>
+        <v>IRS</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>IRS</v>
+        <v>AL 30</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>AL 30</v>
+        <v>GD 30</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>GD 30</v>
+        <v>AL 29</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>AL 29</v>
+        <v>GD29</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>GD29</v>
+        <v>CECO2</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>CECO2</v>
+        <v>ETHA</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>ETHA</v>
+        <v>IBIT</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>IBIT</v>
+        <v>LAC</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>LAC</v>
+        <v>DIVIDENDOS</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>DIVIDENDOS</v>
+        <v>PNZIF</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>PNZIF</v>
+        <v>ASML</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>ASML</v>
+        <v>TEAM</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>TEAM</v>
+        <v>AI</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>AI</v>
+        <v>CLS</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>CLS</v>
+        <v>CEG</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>CEG</v>
+        <v>DECK</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>DECK</v>
+        <v>RGTI</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>RGTI</v>
+        <v>NOW</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>NOW</v>
+        <v>TEM</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>TEM</v>
+        <v>PATH</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>PATH</v>
+        <v>VRTX</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>VRTX</v>
+        <v>VST</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>VST</v>
+        <v>USO</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>USO</v>
+        <v>EFA</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>EFA</v>
+        <v>IEMG</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>IEMG</v>
+        <v>ACWI</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>ACWI</v>
+        <v>GDX</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>GDX</v>
+        <v>HOOD</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>HOOD</v>
+        <v>CRWV</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>CRWV</v>
+        <v>OKLO</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>OKLO</v>
+        <v>RKLB</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>RKLB</v>
+        <v>ALAB</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>ALAB</v>
+        <v>ASTS</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ASTS</v>
+        <v>IREN</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>IREN</v>
+        <v>ECL</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>ECL</v>
+        <v>SPHQ</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>SPHQ</v>
+        <v>EFECTIVO</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>EFECTIVO</v>
+        <v>URA</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>URA</v>
+        <v>COPX</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>COPX</v>
+        <v>ILF</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ILF</v>
+        <v>ESGU</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>ESGU</v>
+        <v>IVV</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>IVV</v>
+        <v>BMNR</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>BMNR</v>
+        <v>BX</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>BX</v>
+        <v>RSP</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>RSP</v>
+        <v>EWI</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>EWI</v>
+        <v>XME</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>XME</v>
+        <v>ICLN</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>ICLN</v>
+        <v>CRWD</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>CRWD</v>
+        <v>ANET</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>ANET</v>
+        <v>O</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>O</v>
+        <v>GLNG</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>GLNG</v>
+        <v>SNDK</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>SNDK</v>
+        <v>NBIS</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>NBIS</v>
+        <v>HIMS</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>HIMS</v>
+        <v>ONDS</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ONDS</v>
+        <v>COP</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>COP</v>
+        <v>NEE</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>NEE</v>
+        <v>MP</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>MP</v>
+        <v>CCJ</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>CCJ</v>
+        <v>FISV</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>FISV</v>
+        <v>KEEL</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>KEEL</v>
+        <v>NVO</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>NVO</v>
+        <v/>
       </c>
     </row>
     <row r="426">
@@ -5346,32 +5346,27 @@
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v/>
+        <v>AGRO.BA</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>AGRO.BA</v>
+        <v>SEMI.BA</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>SEMI.BA</v>
+        <v>EWY</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>EWY</v>
-      </c>
-    </row>
-    <row r="994">
-      <c r="A994" t="str">
         <v>SPCX</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A994"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A993"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A993"/>
+  <dimension ref="A1:A994"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5364,9 +5364,14 @@
         <v>SPCX</v>
       </c>
     </row>
+    <row r="994">
+      <c r="A994" t="str">
+        <v>BRK-B</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A993"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A994"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A994"/>
+  <dimension ref="A1:A995"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5369,9 +5369,14 @@
         <v>BRK-B</v>
       </c>
     </row>
+    <row r="995">
+      <c r="A995" t="str">
+        <v>TQQQ</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A994"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A995"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A995"/>
+  <dimension ref="A1:A996"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5374,9 +5374,14 @@
         <v>TQQQ</v>
       </c>
     </row>
+    <row r="996">
+      <c r="A996" t="str">
+        <v>GEV</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A995"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A996"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tickers.xlsx
+++ b/data/tickers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A996"/>
+  <dimension ref="A1:A997"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5379,9 +5379,14 @@
         <v>GEV</v>
       </c>
     </row>
+    <row r="997">
+      <c r="A997" t="str">
+        <v>DELL</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A996"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A997"/>
   </ignoredErrors>
 </worksheet>
 </file>